--- a/docs/reproducibility_assessment.xlsx
+++ b/docs/reproducibility_assessment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AminD\OneDrive\Desktop\Work\Fraunhofer Job\Work\Code\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7D648C-1C53-4B19-9C90-B1698DA91826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DE8896-9A89-4CC9-B500-306CBBA0289B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="129">
   <si>
     <t>Paper Title</t>
   </si>
@@ -42,16 +42,6 @@
 Options: GIT REPO  |  PYPI PACKAGE  |  CONDA PACKAGE  |  HUGGINGFACE INTEGRATION  |  OTHER PACKAGE MANAGER  |  DOCKER CONTAINER  |  NOT APPLICABLE</t>
   </si>
   <si>
-    <t>5.2.2 — Maintenance Activity Indicators  [Multi-select]
-Options: RECENT COMMITS (&lt;6 months)  |  ACTIVE ISSUE RESPONSES  |  MULTIPLE CONTRIBUTORS  |  VERSIONED RELEASES  |  STALE (&gt;1 year)  |  ARCHIVED  |  NOT ASSESSABLE</t>
-  </si>
-  <si>
-    <t>5.2.3 — Adoption Metrics  [Free Text]</t>
-  </si>
-  <si>
-    <t>5.2.4 — Post-Publication Maintenance  [Free Text]</t>
-  </si>
-  <si>
     <t>5.3.3 — Data Splits and Raw Artifacts  [Multi-select]
 Options: SPLITS SHARED  |  INTERMEDIATE RESULTS  |  NONE</t>
   </si>
@@ -124,27 +114,6 @@
   </si>
   <si>
     <t>NOT APPLICABLE</t>
-  </si>
-  <si>
-    <t>RECENT COMMITS (&lt;6 months)</t>
-  </si>
-  <si>
-    <t>ACTIVE ISSUE RESPONSES</t>
-  </si>
-  <si>
-    <t>MULTIPLE CONTRIBUTORS</t>
-  </si>
-  <si>
-    <t>VERSIONED RELEASES</t>
-  </si>
-  <si>
-    <t>STALE (&gt;1 year)</t>
-  </si>
-  <si>
-    <t>ARCHIVED</t>
-  </si>
-  <si>
-    <t>NOT ASSESSABLE</t>
   </si>
   <si>
     <t>SPLITS SHARED</t>
@@ -1137,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CJ32"/>
+  <dimension ref="A1:BR32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1152,26 +1121,20 @@
     <col min="21" max="23" width="32" customWidth="1"/>
     <col min="24" max="30" width="16" customWidth="1"/>
     <col min="31" max="33" width="32" customWidth="1"/>
-    <col min="34" max="40" width="16" customWidth="1"/>
-    <col min="41" max="43" width="32" customWidth="1"/>
-    <col min="44" max="44" width="16" customWidth="1"/>
-    <col min="45" max="47" width="32" customWidth="1"/>
-    <col min="48" max="48" width="16" customWidth="1"/>
-    <col min="49" max="51" width="32" customWidth="1"/>
-    <col min="52" max="54" width="16" customWidth="1"/>
-    <col min="55" max="57" width="32" customWidth="1"/>
-    <col min="58" max="63" width="16" customWidth="1"/>
-    <col min="64" max="66" width="32" customWidth="1"/>
-    <col min="67" max="67" width="16" customWidth="1"/>
-    <col min="68" max="70" width="32" customWidth="1"/>
-    <col min="71" max="75" width="16" customWidth="1"/>
-    <col min="76" max="78" width="32" customWidth="1"/>
-    <col min="79" max="79" width="16" customWidth="1"/>
-    <col min="80" max="82" width="32" customWidth="1"/>
-    <col min="83" max="88" width="16" customWidth="1"/>
+    <col min="34" max="36" width="16" customWidth="1"/>
+    <col min="37" max="39" width="32" customWidth="1"/>
+    <col min="40" max="45" width="16" customWidth="1"/>
+    <col min="46" max="48" width="32" customWidth="1"/>
+    <col min="49" max="49" width="16" customWidth="1"/>
+    <col min="50" max="52" width="32" customWidth="1"/>
+    <col min="53" max="57" width="16" customWidth="1"/>
+    <col min="58" max="60" width="32" customWidth="1"/>
+    <col min="61" max="61" width="16" customWidth="1"/>
+    <col min="62" max="64" width="32" customWidth="1"/>
+    <col min="65" max="70" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -1182,7 +1145,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E1" s="19"/>
       <c r="F1" s="20"/>
@@ -1223,337 +1186,259 @@
       <c r="AG1" s="20"/>
       <c r="AH1" s="21"/>
       <c r="AI1" s="21"/>
-      <c r="AJ1" s="21"/>
-      <c r="AK1" s="21"/>
-      <c r="AL1" s="21"/>
-      <c r="AM1" s="21"/>
-      <c r="AN1" s="22"/>
-      <c r="AO1" s="18" t="s">
+      <c r="AJ1" s="22"/>
+      <c r="AK1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="AP1" s="19"/>
-      <c r="AQ1" s="20"/>
-      <c r="AR1" s="22"/>
-      <c r="AS1" s="18" t="s">
+      <c r="AL1" s="19"/>
+      <c r="AM1" s="20"/>
+      <c r="AN1" s="21"/>
+      <c r="AO1" s="21"/>
+      <c r="AP1" s="21"/>
+      <c r="AQ1" s="21"/>
+      <c r="AR1" s="21"/>
+      <c r="AS1" s="22"/>
+      <c r="AT1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="AT1" s="19"/>
-      <c r="AU1" s="20"/>
-      <c r="AV1" s="22"/>
-      <c r="AW1" s="18" t="s">
+      <c r="AU1" s="19"/>
+      <c r="AV1" s="20"/>
+      <c r="AW1" s="22"/>
+      <c r="AX1" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="AX1" s="19"/>
-      <c r="AY1" s="20"/>
-      <c r="AZ1" s="21"/>
+      <c r="AY1" s="19"/>
+      <c r="AZ1" s="20"/>
       <c r="BA1" s="21"/>
-      <c r="BB1" s="22"/>
-      <c r="BC1" s="18" t="s">
+      <c r="BB1" s="21"/>
+      <c r="BC1" s="21"/>
+      <c r="BD1" s="21"/>
+      <c r="BE1" s="22"/>
+      <c r="BF1" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="BD1" s="19"/>
-      <c r="BE1" s="20"/>
-      <c r="BF1" s="21"/>
-      <c r="BG1" s="21"/>
-      <c r="BH1" s="21"/>
-      <c r="BI1" s="21"/>
-      <c r="BJ1" s="21"/>
-      <c r="BK1" s="22"/>
-      <c r="BL1" s="18" t="s">
+      <c r="BG1" s="19"/>
+      <c r="BH1" s="20"/>
+      <c r="BI1" s="22"/>
+      <c r="BJ1" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="BM1" s="19"/>
-      <c r="BN1" s="20"/>
-      <c r="BO1" s="22"/>
-      <c r="BP1" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="BQ1" s="19"/>
-      <c r="BR1" s="20"/>
-      <c r="BS1" s="21"/>
-      <c r="BT1" s="21"/>
-      <c r="BU1" s="21"/>
-      <c r="BV1" s="21"/>
-      <c r="BW1" s="22"/>
-      <c r="BX1" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="BY1" s="19"/>
-      <c r="BZ1" s="20"/>
-      <c r="CA1" s="22"/>
-      <c r="CB1" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="CC1" s="19"/>
-      <c r="CD1" s="20"/>
-      <c r="CE1" s="21"/>
-      <c r="CF1" s="21"/>
-      <c r="CG1" s="21"/>
-      <c r="CH1" s="21"/>
-      <c r="CI1" s="21"/>
-      <c r="CJ1" s="22"/>
+      <c r="BK1" s="19"/>
+      <c r="BL1" s="20"/>
+      <c r="BM1" s="21"/>
+      <c r="BN1" s="21"/>
+      <c r="BO1" s="21"/>
+      <c r="BP1" s="21"/>
+      <c r="BQ1" s="21"/>
+      <c r="BR1" s="22"/>
     </row>
-    <row r="2" spans="1:88" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:70" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28"/>
       <c r="B2" s="28"/>
       <c r="C2" s="32"/>
       <c r="D2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="H2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="L2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="M2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="N2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="R2" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="T2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="3" t="s">
+      <c r="U2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="V2" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="W2" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="X2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="Y2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Z2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="16" t="s">
+      <c r="AA2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF2" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG2" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL2" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM2" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AQ2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AT2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="AU2" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="AV2" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="AW2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="S2" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="T2" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="U2" s="16" t="s">
+      <c r="AX2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="AY2" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="AZ2" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="BA2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="BB2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="BC2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BD2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="BE2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="BF2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="BG2" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="BH2" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="BI2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="V2" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="W2" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA2" s="3" t="s">
+      <c r="BJ2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="BK2" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="BL2" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="BM2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="BN2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BO2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="BP2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="BQ2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="BR2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AB2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="AE2" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF2" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG2" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AH2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AK2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AN2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO2" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="AP2" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="AQ2" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AR2" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="AS2" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="AT2" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="AU2" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AV2" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="AW2" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="AX2" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="AY2" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AZ2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="BA2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="BB2" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="BC2" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="BD2" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="BE2" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="BF2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="BG2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="BH2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="BI2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="BK2" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="BL2" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="BM2" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="BN2" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="BO2" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="BP2" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="BQ2" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="BR2" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="BS2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="BT2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="BU2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="BV2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="BW2" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="BX2" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="BY2" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="BZ2" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="CA2" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="CB2" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="CC2" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="CD2" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="CE2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="CF2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="CG2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="CH2" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="CI2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="CJ2" s="4" t="s">
-        <v>31</v>
-      </c>
     </row>
-    <row r="3" spans="1:88" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:70" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="24"/>
       <c r="B3" s="24"/>
       <c r="C3" s="33"/>
@@ -1565,22 +1450,22 @@
       <c r="I3" s="24"/>
       <c r="J3" s="26"/>
       <c r="K3" s="6" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="Q3" s="17"/>
       <c r="R3" s="24"/>
@@ -1590,148 +1475,116 @@
       <c r="V3" s="24"/>
       <c r="W3" s="26"/>
       <c r="X3" s="6" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="AB3" s="6" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="AC3" s="6" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="AE3" s="17"/>
       <c r="AF3" s="24"/>
       <c r="AG3" s="26"/>
       <c r="AH3" s="6" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="AI3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AJ3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AK3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AL3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AM3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AN3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AO3" s="17"/>
-      <c r="AP3" s="24"/>
-      <c r="AQ3" s="26"/>
-      <c r="AR3" s="30"/>
-      <c r="AS3" s="17"/>
-      <c r="AT3" s="24"/>
-      <c r="AU3" s="26"/>
-      <c r="AV3" s="30"/>
-      <c r="AW3" s="17"/>
-      <c r="AX3" s="24"/>
-      <c r="AY3" s="26"/>
-      <c r="AZ3" s="6" t="s">
-        <v>57</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK3" s="17"/>
+      <c r="AL3" s="24"/>
+      <c r="AM3" s="26"/>
+      <c r="AN3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AO3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AP3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AQ3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AR3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT3" s="17"/>
+      <c r="AU3" s="24"/>
+      <c r="AV3" s="26"/>
+      <c r="AW3" s="30"/>
+      <c r="AX3" s="17"/>
+      <c r="AY3" s="24"/>
+      <c r="AZ3" s="26"/>
       <c r="BA3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="BB3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="BC3" s="17"/>
-      <c r="BD3" s="24"/>
-      <c r="BE3" s="26"/>
-      <c r="BF3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="BG3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="BH3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="BI3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="BJ3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="BK3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="BL3" s="17"/>
-      <c r="BM3" s="24"/>
-      <c r="BN3" s="26"/>
-      <c r="BO3" s="30"/>
-      <c r="BP3" s="17"/>
-      <c r="BQ3" s="24"/>
-      <c r="BR3" s="26"/>
-      <c r="BS3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="BT3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="BU3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="BV3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="BW3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="BX3" s="17"/>
-      <c r="BY3" s="24"/>
-      <c r="BZ3" s="26"/>
-      <c r="CA3" s="30"/>
-      <c r="CB3" s="17"/>
-      <c r="CC3" s="24"/>
-      <c r="CD3" s="26"/>
-      <c r="CE3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="CF3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="CG3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="CH3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="CI3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="CJ3" s="1" t="s">
-        <v>57</v>
+        <v>47</v>
+      </c>
+      <c r="BB3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="BC3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="BD3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="BE3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="BF3" s="17"/>
+      <c r="BG3" s="24"/>
+      <c r="BH3" s="26"/>
+      <c r="BI3" s="30"/>
+      <c r="BJ3" s="17"/>
+      <c r="BK3" s="24"/>
+      <c r="BL3" s="26"/>
+      <c r="BM3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="BN3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="BO3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="BP3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="BQ3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="BR3" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="10"/>
@@ -1765,69 +1618,51 @@
       <c r="AG4" s="11"/>
       <c r="AH4" s="13"/>
       <c r="AI4" s="14"/>
-      <c r="AJ4" s="13"/>
-      <c r="AK4" s="14"/>
-      <c r="AL4" s="13"/>
-      <c r="AM4" s="14"/>
-      <c r="AN4" s="12"/>
-      <c r="AO4" s="9"/>
-      <c r="AP4" s="10"/>
-      <c r="AQ4" s="11"/>
-      <c r="AR4" s="12"/>
-      <c r="AS4" s="9"/>
-      <c r="AT4" s="10"/>
-      <c r="AU4" s="11"/>
-      <c r="AV4" s="12"/>
-      <c r="AW4" s="9"/>
-      <c r="AX4" s="10"/>
-      <c r="AY4" s="11"/>
-      <c r="AZ4" s="13"/>
-      <c r="BA4" s="14"/>
-      <c r="BB4" s="12"/>
-      <c r="BC4" s="9"/>
-      <c r="BD4" s="10"/>
-      <c r="BE4" s="11"/>
-      <c r="BF4" s="13"/>
-      <c r="BG4" s="14"/>
-      <c r="BH4" s="13"/>
-      <c r="BI4" s="14"/>
-      <c r="BJ4" s="13"/>
-      <c r="BK4" s="15"/>
-      <c r="BL4" s="9"/>
-      <c r="BM4" s="10"/>
-      <c r="BN4" s="11"/>
-      <c r="BO4" s="12"/>
-      <c r="BP4" s="9"/>
-      <c r="BQ4" s="10"/>
-      <c r="BR4" s="11"/>
-      <c r="BS4" s="13"/>
-      <c r="BT4" s="14"/>
-      <c r="BU4" s="13"/>
-      <c r="BV4" s="14"/>
-      <c r="BW4" s="12"/>
-      <c r="BX4" s="9"/>
-      <c r="BY4" s="10"/>
-      <c r="BZ4" s="11"/>
-      <c r="CA4" s="12"/>
-      <c r="CB4" s="9"/>
-      <c r="CC4" s="10"/>
-      <c r="CD4" s="11"/>
-      <c r="CE4" s="13"/>
-      <c r="CF4" s="14"/>
-      <c r="CG4" s="13"/>
-      <c r="CH4" s="14"/>
-      <c r="CI4" s="13"/>
-      <c r="CJ4" s="15"/>
+      <c r="AJ4" s="12"/>
+      <c r="AK4" s="9"/>
+      <c r="AL4" s="10"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="13"/>
+      <c r="AO4" s="14"/>
+      <c r="AP4" s="13"/>
+      <c r="AQ4" s="14"/>
+      <c r="AR4" s="13"/>
+      <c r="AS4" s="15"/>
+      <c r="AT4" s="9"/>
+      <c r="AU4" s="10"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="12"/>
+      <c r="AX4" s="9"/>
+      <c r="AY4" s="10"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="13"/>
+      <c r="BB4" s="14"/>
+      <c r="BC4" s="13"/>
+      <c r="BD4" s="14"/>
+      <c r="BE4" s="12"/>
+      <c r="BF4" s="9"/>
+      <c r="BG4" s="10"/>
+      <c r="BH4" s="11"/>
+      <c r="BI4" s="12"/>
+      <c r="BJ4" s="9"/>
+      <c r="BK4" s="10"/>
+      <c r="BL4" s="11"/>
+      <c r="BM4" s="13"/>
+      <c r="BN4" s="14"/>
+      <c r="BO4" s="13"/>
+      <c r="BP4" s="14"/>
+      <c r="BQ4" s="13"/>
+      <c r="BR4" s="15"/>
     </row>
-    <row r="5" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
@@ -1861,69 +1696,51 @@
       <c r="AG5" s="11"/>
       <c r="AH5" s="13"/>
       <c r="AI5" s="14"/>
-      <c r="AJ5" s="13"/>
-      <c r="AK5" s="14"/>
-      <c r="AL5" s="13"/>
-      <c r="AM5" s="14"/>
-      <c r="AN5" s="12"/>
-      <c r="AO5" s="9"/>
-      <c r="AP5" s="10"/>
-      <c r="AQ5" s="11"/>
-      <c r="AR5" s="12"/>
-      <c r="AS5" s="9"/>
-      <c r="AT5" s="10"/>
-      <c r="AU5" s="11"/>
-      <c r="AV5" s="12"/>
-      <c r="AW5" s="9"/>
-      <c r="AX5" s="10"/>
-      <c r="AY5" s="11"/>
-      <c r="AZ5" s="13"/>
-      <c r="BA5" s="14"/>
-      <c r="BB5" s="12"/>
-      <c r="BC5" s="9"/>
-      <c r="BD5" s="10"/>
-      <c r="BE5" s="11"/>
-      <c r="BF5" s="13"/>
-      <c r="BG5" s="14"/>
-      <c r="BH5" s="13"/>
-      <c r="BI5" s="14"/>
-      <c r="BJ5" s="13"/>
-      <c r="BK5" s="15"/>
-      <c r="BL5" s="9"/>
-      <c r="BM5" s="10"/>
-      <c r="BN5" s="11"/>
-      <c r="BO5" s="12"/>
-      <c r="BP5" s="9"/>
-      <c r="BQ5" s="10"/>
-      <c r="BR5" s="11"/>
-      <c r="BS5" s="13"/>
-      <c r="BT5" s="14"/>
-      <c r="BU5" s="13"/>
-      <c r="BV5" s="14"/>
-      <c r="BW5" s="12"/>
-      <c r="BX5" s="9"/>
-      <c r="BY5" s="10"/>
-      <c r="BZ5" s="11"/>
-      <c r="CA5" s="12"/>
-      <c r="CB5" s="9"/>
-      <c r="CC5" s="10"/>
-      <c r="CD5" s="11"/>
-      <c r="CE5" s="13"/>
-      <c r="CF5" s="14"/>
-      <c r="CG5" s="13"/>
-      <c r="CH5" s="14"/>
-      <c r="CI5" s="13"/>
-      <c r="CJ5" s="15"/>
+      <c r="AJ5" s="12"/>
+      <c r="AK5" s="9"/>
+      <c r="AL5" s="10"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="13"/>
+      <c r="AO5" s="14"/>
+      <c r="AP5" s="13"/>
+      <c r="AQ5" s="14"/>
+      <c r="AR5" s="13"/>
+      <c r="AS5" s="15"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="10"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="12"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="10"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="13"/>
+      <c r="BB5" s="14"/>
+      <c r="BC5" s="13"/>
+      <c r="BD5" s="14"/>
+      <c r="BE5" s="12"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="10"/>
+      <c r="BH5" s="11"/>
+      <c r="BI5" s="12"/>
+      <c r="BJ5" s="9"/>
+      <c r="BK5" s="10"/>
+      <c r="BL5" s="11"/>
+      <c r="BM5" s="13"/>
+      <c r="BN5" s="14"/>
+      <c r="BO5" s="13"/>
+      <c r="BP5" s="14"/>
+      <c r="BQ5" s="13"/>
+      <c r="BR5" s="15"/>
     </row>
-    <row r="6" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10"/>
@@ -1957,69 +1774,51 @@
       <c r="AG6" s="11"/>
       <c r="AH6" s="13"/>
       <c r="AI6" s="14"/>
-      <c r="AJ6" s="13"/>
-      <c r="AK6" s="14"/>
-      <c r="AL6" s="13"/>
-      <c r="AM6" s="14"/>
-      <c r="AN6" s="12"/>
-      <c r="AO6" s="9"/>
-      <c r="AP6" s="10"/>
-      <c r="AQ6" s="11"/>
-      <c r="AR6" s="12"/>
-      <c r="AS6" s="9"/>
-      <c r="AT6" s="10"/>
-      <c r="AU6" s="11"/>
-      <c r="AV6" s="12"/>
-      <c r="AW6" s="9"/>
-      <c r="AX6" s="10"/>
-      <c r="AY6" s="11"/>
-      <c r="AZ6" s="13"/>
-      <c r="BA6" s="14"/>
-      <c r="BB6" s="12"/>
-      <c r="BC6" s="9"/>
-      <c r="BD6" s="10"/>
-      <c r="BE6" s="11"/>
-      <c r="BF6" s="13"/>
-      <c r="BG6" s="14"/>
-      <c r="BH6" s="13"/>
-      <c r="BI6" s="14"/>
-      <c r="BJ6" s="13"/>
-      <c r="BK6" s="15"/>
-      <c r="BL6" s="9"/>
-      <c r="BM6" s="10"/>
-      <c r="BN6" s="11"/>
-      <c r="BO6" s="12"/>
-      <c r="BP6" s="9"/>
-      <c r="BQ6" s="10"/>
-      <c r="BR6" s="11"/>
-      <c r="BS6" s="13"/>
-      <c r="BT6" s="14"/>
-      <c r="BU6" s="13"/>
-      <c r="BV6" s="14"/>
-      <c r="BW6" s="12"/>
-      <c r="BX6" s="9"/>
-      <c r="BY6" s="10"/>
-      <c r="BZ6" s="11"/>
-      <c r="CA6" s="12"/>
-      <c r="CB6" s="9"/>
-      <c r="CC6" s="10"/>
-      <c r="CD6" s="11"/>
-      <c r="CE6" s="13"/>
-      <c r="CF6" s="14"/>
-      <c r="CG6" s="13"/>
-      <c r="CH6" s="14"/>
-      <c r="CI6" s="13"/>
-      <c r="CJ6" s="15"/>
+      <c r="AJ6" s="12"/>
+      <c r="AK6" s="9"/>
+      <c r="AL6" s="10"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="13"/>
+      <c r="AO6" s="14"/>
+      <c r="AP6" s="13"/>
+      <c r="AQ6" s="14"/>
+      <c r="AR6" s="13"/>
+      <c r="AS6" s="15"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="10"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="12"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="10"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="13"/>
+      <c r="BB6" s="14"/>
+      <c r="BC6" s="13"/>
+      <c r="BD6" s="14"/>
+      <c r="BE6" s="12"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="10"/>
+      <c r="BH6" s="11"/>
+      <c r="BI6" s="12"/>
+      <c r="BJ6" s="9"/>
+      <c r="BK6" s="10"/>
+      <c r="BL6" s="11"/>
+      <c r="BM6" s="13"/>
+      <c r="BN6" s="14"/>
+      <c r="BO6" s="13"/>
+      <c r="BP6" s="14"/>
+      <c r="BQ6" s="13"/>
+      <c r="BR6" s="15"/>
     </row>
-    <row r="7" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="10"/>
@@ -2053,69 +1852,51 @@
       <c r="AG7" s="11"/>
       <c r="AH7" s="13"/>
       <c r="AI7" s="14"/>
-      <c r="AJ7" s="13"/>
-      <c r="AK7" s="14"/>
-      <c r="AL7" s="13"/>
-      <c r="AM7" s="14"/>
-      <c r="AN7" s="12"/>
-      <c r="AO7" s="9"/>
-      <c r="AP7" s="10"/>
-      <c r="AQ7" s="11"/>
-      <c r="AR7" s="12"/>
-      <c r="AS7" s="9"/>
-      <c r="AT7" s="10"/>
-      <c r="AU7" s="11"/>
-      <c r="AV7" s="12"/>
-      <c r="AW7" s="9"/>
-      <c r="AX7" s="10"/>
-      <c r="AY7" s="11"/>
-      <c r="AZ7" s="13"/>
-      <c r="BA7" s="14"/>
-      <c r="BB7" s="12"/>
-      <c r="BC7" s="9"/>
-      <c r="BD7" s="10"/>
-      <c r="BE7" s="11"/>
-      <c r="BF7" s="13"/>
-      <c r="BG7" s="14"/>
-      <c r="BH7" s="13"/>
-      <c r="BI7" s="14"/>
-      <c r="BJ7" s="13"/>
-      <c r="BK7" s="15"/>
-      <c r="BL7" s="9"/>
-      <c r="BM7" s="10"/>
-      <c r="BN7" s="11"/>
-      <c r="BO7" s="12"/>
-      <c r="BP7" s="9"/>
-      <c r="BQ7" s="10"/>
-      <c r="BR7" s="11"/>
-      <c r="BS7" s="13"/>
-      <c r="BT7" s="14"/>
-      <c r="BU7" s="13"/>
-      <c r="BV7" s="14"/>
-      <c r="BW7" s="12"/>
-      <c r="BX7" s="9"/>
-      <c r="BY7" s="10"/>
-      <c r="BZ7" s="11"/>
-      <c r="CA7" s="12"/>
-      <c r="CB7" s="9"/>
-      <c r="CC7" s="10"/>
-      <c r="CD7" s="11"/>
-      <c r="CE7" s="13"/>
-      <c r="CF7" s="14"/>
-      <c r="CG7" s="13"/>
-      <c r="CH7" s="14"/>
-      <c r="CI7" s="13"/>
-      <c r="CJ7" s="15"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="9"/>
+      <c r="AL7" s="10"/>
+      <c r="AM7" s="11"/>
+      <c r="AN7" s="13"/>
+      <c r="AO7" s="14"/>
+      <c r="AP7" s="13"/>
+      <c r="AQ7" s="14"/>
+      <c r="AR7" s="13"/>
+      <c r="AS7" s="15"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="10"/>
+      <c r="AV7" s="11"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="10"/>
+      <c r="AZ7" s="11"/>
+      <c r="BA7" s="13"/>
+      <c r="BB7" s="14"/>
+      <c r="BC7" s="13"/>
+      <c r="BD7" s="14"/>
+      <c r="BE7" s="12"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="10"/>
+      <c r="BH7" s="11"/>
+      <c r="BI7" s="12"/>
+      <c r="BJ7" s="9"/>
+      <c r="BK7" s="10"/>
+      <c r="BL7" s="11"/>
+      <c r="BM7" s="13"/>
+      <c r="BN7" s="14"/>
+      <c r="BO7" s="13"/>
+      <c r="BP7" s="14"/>
+      <c r="BQ7" s="13"/>
+      <c r="BR7" s="15"/>
     </row>
-    <row r="8" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="10"/>
@@ -2149,69 +1930,51 @@
       <c r="AG8" s="11"/>
       <c r="AH8" s="13"/>
       <c r="AI8" s="14"/>
-      <c r="AJ8" s="13"/>
-      <c r="AK8" s="14"/>
-      <c r="AL8" s="13"/>
-      <c r="AM8" s="14"/>
-      <c r="AN8" s="12"/>
-      <c r="AO8" s="9"/>
-      <c r="AP8" s="10"/>
-      <c r="AQ8" s="11"/>
-      <c r="AR8" s="12"/>
-      <c r="AS8" s="9"/>
-      <c r="AT8" s="10"/>
-      <c r="AU8" s="11"/>
-      <c r="AV8" s="12"/>
-      <c r="AW8" s="9"/>
-      <c r="AX8" s="10"/>
-      <c r="AY8" s="11"/>
-      <c r="AZ8" s="13"/>
-      <c r="BA8" s="14"/>
-      <c r="BB8" s="12"/>
-      <c r="BC8" s="9"/>
-      <c r="BD8" s="10"/>
-      <c r="BE8" s="11"/>
-      <c r="BF8" s="13"/>
-      <c r="BG8" s="14"/>
-      <c r="BH8" s="13"/>
-      <c r="BI8" s="14"/>
-      <c r="BJ8" s="13"/>
-      <c r="BK8" s="15"/>
-      <c r="BL8" s="9"/>
-      <c r="BM8" s="10"/>
-      <c r="BN8" s="11"/>
-      <c r="BO8" s="12"/>
-      <c r="BP8" s="9"/>
-      <c r="BQ8" s="10"/>
-      <c r="BR8" s="11"/>
-      <c r="BS8" s="13"/>
-      <c r="BT8" s="14"/>
-      <c r="BU8" s="13"/>
-      <c r="BV8" s="14"/>
-      <c r="BW8" s="12"/>
-      <c r="BX8" s="9"/>
-      <c r="BY8" s="10"/>
-      <c r="BZ8" s="11"/>
-      <c r="CA8" s="12"/>
-      <c r="CB8" s="9"/>
-      <c r="CC8" s="10"/>
-      <c r="CD8" s="11"/>
-      <c r="CE8" s="13"/>
-      <c r="CF8" s="14"/>
-      <c r="CG8" s="13"/>
-      <c r="CH8" s="14"/>
-      <c r="CI8" s="13"/>
-      <c r="CJ8" s="15"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="9"/>
+      <c r="AL8" s="10"/>
+      <c r="AM8" s="11"/>
+      <c r="AN8" s="13"/>
+      <c r="AO8" s="14"/>
+      <c r="AP8" s="13"/>
+      <c r="AQ8" s="14"/>
+      <c r="AR8" s="13"/>
+      <c r="AS8" s="15"/>
+      <c r="AT8" s="9"/>
+      <c r="AU8" s="10"/>
+      <c r="AV8" s="11"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="9"/>
+      <c r="AY8" s="10"/>
+      <c r="AZ8" s="11"/>
+      <c r="BA8" s="13"/>
+      <c r="BB8" s="14"/>
+      <c r="BC8" s="13"/>
+      <c r="BD8" s="14"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="9"/>
+      <c r="BG8" s="10"/>
+      <c r="BH8" s="11"/>
+      <c r="BI8" s="12"/>
+      <c r="BJ8" s="9"/>
+      <c r="BK8" s="10"/>
+      <c r="BL8" s="11"/>
+      <c r="BM8" s="13"/>
+      <c r="BN8" s="14"/>
+      <c r="BO8" s="13"/>
+      <c r="BP8" s="14"/>
+      <c r="BQ8" s="13"/>
+      <c r="BR8" s="15"/>
     </row>
-    <row r="9" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="10"/>
@@ -2245,69 +2008,51 @@
       <c r="AG9" s="11"/>
       <c r="AH9" s="13"/>
       <c r="AI9" s="14"/>
-      <c r="AJ9" s="13"/>
-      <c r="AK9" s="14"/>
-      <c r="AL9" s="13"/>
-      <c r="AM9" s="14"/>
-      <c r="AN9" s="12"/>
-      <c r="AO9" s="9"/>
-      <c r="AP9" s="10"/>
-      <c r="AQ9" s="11"/>
-      <c r="AR9" s="12"/>
-      <c r="AS9" s="9"/>
-      <c r="AT9" s="10"/>
-      <c r="AU9" s="11"/>
-      <c r="AV9" s="12"/>
-      <c r="AW9" s="9"/>
-      <c r="AX9" s="10"/>
-      <c r="AY9" s="11"/>
-      <c r="AZ9" s="13"/>
-      <c r="BA9" s="14"/>
-      <c r="BB9" s="12"/>
-      <c r="BC9" s="9"/>
-      <c r="BD9" s="10"/>
-      <c r="BE9" s="11"/>
-      <c r="BF9" s="13"/>
-      <c r="BG9" s="14"/>
-      <c r="BH9" s="13"/>
-      <c r="BI9" s="14"/>
-      <c r="BJ9" s="13"/>
-      <c r="BK9" s="15"/>
-      <c r="BL9" s="9"/>
-      <c r="BM9" s="10"/>
-      <c r="BN9" s="11"/>
-      <c r="BO9" s="12"/>
-      <c r="BP9" s="9"/>
-      <c r="BQ9" s="10"/>
-      <c r="BR9" s="11"/>
-      <c r="BS9" s="13"/>
-      <c r="BT9" s="14"/>
-      <c r="BU9" s="13"/>
-      <c r="BV9" s="14"/>
-      <c r="BW9" s="12"/>
-      <c r="BX9" s="9"/>
-      <c r="BY9" s="10"/>
-      <c r="BZ9" s="11"/>
-      <c r="CA9" s="12"/>
-      <c r="CB9" s="9"/>
-      <c r="CC9" s="10"/>
-      <c r="CD9" s="11"/>
-      <c r="CE9" s="13"/>
-      <c r="CF9" s="14"/>
-      <c r="CG9" s="13"/>
-      <c r="CH9" s="14"/>
-      <c r="CI9" s="13"/>
-      <c r="CJ9" s="15"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="9"/>
+      <c r="AL9" s="10"/>
+      <c r="AM9" s="11"/>
+      <c r="AN9" s="13"/>
+      <c r="AO9" s="14"/>
+      <c r="AP9" s="13"/>
+      <c r="AQ9" s="14"/>
+      <c r="AR9" s="13"/>
+      <c r="AS9" s="15"/>
+      <c r="AT9" s="9"/>
+      <c r="AU9" s="10"/>
+      <c r="AV9" s="11"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="9"/>
+      <c r="AY9" s="10"/>
+      <c r="AZ9" s="11"/>
+      <c r="BA9" s="13"/>
+      <c r="BB9" s="14"/>
+      <c r="BC9" s="13"/>
+      <c r="BD9" s="14"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="9"/>
+      <c r="BG9" s="10"/>
+      <c r="BH9" s="11"/>
+      <c r="BI9" s="12"/>
+      <c r="BJ9" s="9"/>
+      <c r="BK9" s="10"/>
+      <c r="BL9" s="11"/>
+      <c r="BM9" s="13"/>
+      <c r="BN9" s="14"/>
+      <c r="BO9" s="13"/>
+      <c r="BP9" s="14"/>
+      <c r="BQ9" s="13"/>
+      <c r="BR9" s="15"/>
     </row>
-    <row r="10" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="10"/>
@@ -2341,69 +2086,51 @@
       <c r="AG10" s="11"/>
       <c r="AH10" s="13"/>
       <c r="AI10" s="14"/>
-      <c r="AJ10" s="13"/>
-      <c r="AK10" s="14"/>
-      <c r="AL10" s="13"/>
-      <c r="AM10" s="14"/>
-      <c r="AN10" s="12"/>
-      <c r="AO10" s="9"/>
-      <c r="AP10" s="10"/>
-      <c r="AQ10" s="11"/>
-      <c r="AR10" s="12"/>
-      <c r="AS10" s="9"/>
-      <c r="AT10" s="10"/>
-      <c r="AU10" s="11"/>
-      <c r="AV10" s="12"/>
-      <c r="AW10" s="9"/>
-      <c r="AX10" s="10"/>
-      <c r="AY10" s="11"/>
-      <c r="AZ10" s="13"/>
-      <c r="BA10" s="14"/>
-      <c r="BB10" s="12"/>
-      <c r="BC10" s="9"/>
-      <c r="BD10" s="10"/>
-      <c r="BE10" s="11"/>
-      <c r="BF10" s="13"/>
-      <c r="BG10" s="14"/>
-      <c r="BH10" s="13"/>
-      <c r="BI10" s="14"/>
-      <c r="BJ10" s="13"/>
-      <c r="BK10" s="15"/>
-      <c r="BL10" s="9"/>
-      <c r="BM10" s="10"/>
-      <c r="BN10" s="11"/>
-      <c r="BO10" s="12"/>
-      <c r="BP10" s="9"/>
-      <c r="BQ10" s="10"/>
-      <c r="BR10" s="11"/>
-      <c r="BS10" s="13"/>
-      <c r="BT10" s="14"/>
-      <c r="BU10" s="13"/>
-      <c r="BV10" s="14"/>
-      <c r="BW10" s="12"/>
-      <c r="BX10" s="9"/>
-      <c r="BY10" s="10"/>
-      <c r="BZ10" s="11"/>
-      <c r="CA10" s="12"/>
-      <c r="CB10" s="9"/>
-      <c r="CC10" s="10"/>
-      <c r="CD10" s="11"/>
-      <c r="CE10" s="13"/>
-      <c r="CF10" s="14"/>
-      <c r="CG10" s="13"/>
-      <c r="CH10" s="14"/>
-      <c r="CI10" s="13"/>
-      <c r="CJ10" s="15"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="9"/>
+      <c r="AL10" s="10"/>
+      <c r="AM10" s="11"/>
+      <c r="AN10" s="13"/>
+      <c r="AO10" s="14"/>
+      <c r="AP10" s="13"/>
+      <c r="AQ10" s="14"/>
+      <c r="AR10" s="13"/>
+      <c r="AS10" s="15"/>
+      <c r="AT10" s="9"/>
+      <c r="AU10" s="10"/>
+      <c r="AV10" s="11"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="9"/>
+      <c r="AY10" s="10"/>
+      <c r="AZ10" s="11"/>
+      <c r="BA10" s="13"/>
+      <c r="BB10" s="14"/>
+      <c r="BC10" s="13"/>
+      <c r="BD10" s="14"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="9"/>
+      <c r="BG10" s="10"/>
+      <c r="BH10" s="11"/>
+      <c r="BI10" s="12"/>
+      <c r="BJ10" s="9"/>
+      <c r="BK10" s="10"/>
+      <c r="BL10" s="11"/>
+      <c r="BM10" s="13"/>
+      <c r="BN10" s="14"/>
+      <c r="BO10" s="13"/>
+      <c r="BP10" s="14"/>
+      <c r="BQ10" s="13"/>
+      <c r="BR10" s="15"/>
     </row>
-    <row r="11" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="10"/>
@@ -2437,69 +2164,51 @@
       <c r="AG11" s="11"/>
       <c r="AH11" s="13"/>
       <c r="AI11" s="14"/>
-      <c r="AJ11" s="13"/>
-      <c r="AK11" s="14"/>
-      <c r="AL11" s="13"/>
-      <c r="AM11" s="14"/>
-      <c r="AN11" s="12"/>
-      <c r="AO11" s="9"/>
-      <c r="AP11" s="10"/>
-      <c r="AQ11" s="11"/>
-      <c r="AR11" s="12"/>
-      <c r="AS11" s="9"/>
-      <c r="AT11" s="10"/>
-      <c r="AU11" s="11"/>
-      <c r="AV11" s="12"/>
-      <c r="AW11" s="9"/>
-      <c r="AX11" s="10"/>
-      <c r="AY11" s="11"/>
-      <c r="AZ11" s="13"/>
-      <c r="BA11" s="14"/>
-      <c r="BB11" s="12"/>
-      <c r="BC11" s="9"/>
-      <c r="BD11" s="10"/>
-      <c r="BE11" s="11"/>
-      <c r="BF11" s="13"/>
-      <c r="BG11" s="14"/>
-      <c r="BH11" s="13"/>
-      <c r="BI11" s="14"/>
-      <c r="BJ11" s="13"/>
-      <c r="BK11" s="15"/>
-      <c r="BL11" s="9"/>
-      <c r="BM11" s="10"/>
-      <c r="BN11" s="11"/>
-      <c r="BO11" s="12"/>
-      <c r="BP11" s="9"/>
-      <c r="BQ11" s="10"/>
-      <c r="BR11" s="11"/>
-      <c r="BS11" s="13"/>
-      <c r="BT11" s="14"/>
-      <c r="BU11" s="13"/>
-      <c r="BV11" s="14"/>
-      <c r="BW11" s="12"/>
-      <c r="BX11" s="9"/>
-      <c r="BY11" s="10"/>
-      <c r="BZ11" s="11"/>
-      <c r="CA11" s="12"/>
-      <c r="CB11" s="9"/>
-      <c r="CC11" s="10"/>
-      <c r="CD11" s="11"/>
-      <c r="CE11" s="13"/>
-      <c r="CF11" s="14"/>
-      <c r="CG11" s="13"/>
-      <c r="CH11" s="14"/>
-      <c r="CI11" s="13"/>
-      <c r="CJ11" s="15"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="9"/>
+      <c r="AL11" s="10"/>
+      <c r="AM11" s="11"/>
+      <c r="AN11" s="13"/>
+      <c r="AO11" s="14"/>
+      <c r="AP11" s="13"/>
+      <c r="AQ11" s="14"/>
+      <c r="AR11" s="13"/>
+      <c r="AS11" s="15"/>
+      <c r="AT11" s="9"/>
+      <c r="AU11" s="10"/>
+      <c r="AV11" s="11"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="9"/>
+      <c r="AY11" s="10"/>
+      <c r="AZ11" s="11"/>
+      <c r="BA11" s="13"/>
+      <c r="BB11" s="14"/>
+      <c r="BC11" s="13"/>
+      <c r="BD11" s="14"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="9"/>
+      <c r="BG11" s="10"/>
+      <c r="BH11" s="11"/>
+      <c r="BI11" s="12"/>
+      <c r="BJ11" s="9"/>
+      <c r="BK11" s="10"/>
+      <c r="BL11" s="11"/>
+      <c r="BM11" s="13"/>
+      <c r="BN11" s="14"/>
+      <c r="BO11" s="13"/>
+      <c r="BP11" s="14"/>
+      <c r="BQ11" s="13"/>
+      <c r="BR11" s="15"/>
     </row>
-    <row r="12" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="10"/>
@@ -2533,69 +2242,51 @@
       <c r="AG12" s="11"/>
       <c r="AH12" s="13"/>
       <c r="AI12" s="14"/>
-      <c r="AJ12" s="13"/>
-      <c r="AK12" s="14"/>
-      <c r="AL12" s="13"/>
-      <c r="AM12" s="14"/>
-      <c r="AN12" s="12"/>
-      <c r="AO12" s="9"/>
-      <c r="AP12" s="10"/>
-      <c r="AQ12" s="11"/>
-      <c r="AR12" s="12"/>
-      <c r="AS12" s="9"/>
-      <c r="AT12" s="10"/>
-      <c r="AU12" s="11"/>
-      <c r="AV12" s="12"/>
-      <c r="AW12" s="9"/>
-      <c r="AX12" s="10"/>
-      <c r="AY12" s="11"/>
-      <c r="AZ12" s="13"/>
-      <c r="BA12" s="14"/>
-      <c r="BB12" s="12"/>
-      <c r="BC12" s="9"/>
-      <c r="BD12" s="10"/>
-      <c r="BE12" s="11"/>
-      <c r="BF12" s="13"/>
-      <c r="BG12" s="14"/>
-      <c r="BH12" s="13"/>
-      <c r="BI12" s="14"/>
-      <c r="BJ12" s="13"/>
-      <c r="BK12" s="15"/>
-      <c r="BL12" s="9"/>
-      <c r="BM12" s="10"/>
-      <c r="BN12" s="11"/>
-      <c r="BO12" s="12"/>
-      <c r="BP12" s="9"/>
-      <c r="BQ12" s="10"/>
-      <c r="BR12" s="11"/>
-      <c r="BS12" s="13"/>
-      <c r="BT12" s="14"/>
-      <c r="BU12" s="13"/>
-      <c r="BV12" s="14"/>
-      <c r="BW12" s="12"/>
-      <c r="BX12" s="9"/>
-      <c r="BY12" s="10"/>
-      <c r="BZ12" s="11"/>
-      <c r="CA12" s="12"/>
-      <c r="CB12" s="9"/>
-      <c r="CC12" s="10"/>
-      <c r="CD12" s="11"/>
-      <c r="CE12" s="13"/>
-      <c r="CF12" s="14"/>
-      <c r="CG12" s="13"/>
-      <c r="CH12" s="14"/>
-      <c r="CI12" s="13"/>
-      <c r="CJ12" s="15"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="9"/>
+      <c r="AL12" s="10"/>
+      <c r="AM12" s="11"/>
+      <c r="AN12" s="13"/>
+      <c r="AO12" s="14"/>
+      <c r="AP12" s="13"/>
+      <c r="AQ12" s="14"/>
+      <c r="AR12" s="13"/>
+      <c r="AS12" s="15"/>
+      <c r="AT12" s="9"/>
+      <c r="AU12" s="10"/>
+      <c r="AV12" s="11"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="9"/>
+      <c r="AY12" s="10"/>
+      <c r="AZ12" s="11"/>
+      <c r="BA12" s="13"/>
+      <c r="BB12" s="14"/>
+      <c r="BC12" s="13"/>
+      <c r="BD12" s="14"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="9"/>
+      <c r="BG12" s="10"/>
+      <c r="BH12" s="11"/>
+      <c r="BI12" s="12"/>
+      <c r="BJ12" s="9"/>
+      <c r="BK12" s="10"/>
+      <c r="BL12" s="11"/>
+      <c r="BM12" s="13"/>
+      <c r="BN12" s="14"/>
+      <c r="BO12" s="13"/>
+      <c r="BP12" s="14"/>
+      <c r="BQ12" s="13"/>
+      <c r="BR12" s="15"/>
     </row>
-    <row r="13" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="10"/>
@@ -2629,69 +2320,51 @@
       <c r="AG13" s="11"/>
       <c r="AH13" s="13"/>
       <c r="AI13" s="14"/>
-      <c r="AJ13" s="13"/>
-      <c r="AK13" s="14"/>
-      <c r="AL13" s="13"/>
-      <c r="AM13" s="14"/>
-      <c r="AN13" s="12"/>
-      <c r="AO13" s="9"/>
-      <c r="AP13" s="10"/>
-      <c r="AQ13" s="11"/>
-      <c r="AR13" s="12"/>
-      <c r="AS13" s="9"/>
-      <c r="AT13" s="10"/>
-      <c r="AU13" s="11"/>
-      <c r="AV13" s="12"/>
-      <c r="AW13" s="9"/>
-      <c r="AX13" s="10"/>
-      <c r="AY13" s="11"/>
-      <c r="AZ13" s="13"/>
-      <c r="BA13" s="14"/>
-      <c r="BB13" s="12"/>
-      <c r="BC13" s="9"/>
-      <c r="BD13" s="10"/>
-      <c r="BE13" s="11"/>
-      <c r="BF13" s="13"/>
-      <c r="BG13" s="14"/>
-      <c r="BH13" s="13"/>
-      <c r="BI13" s="14"/>
-      <c r="BJ13" s="13"/>
-      <c r="BK13" s="15"/>
-      <c r="BL13" s="9"/>
-      <c r="BM13" s="10"/>
-      <c r="BN13" s="11"/>
-      <c r="BO13" s="12"/>
-      <c r="BP13" s="9"/>
-      <c r="BQ13" s="10"/>
-      <c r="BR13" s="11"/>
-      <c r="BS13" s="13"/>
-      <c r="BT13" s="14"/>
-      <c r="BU13" s="13"/>
-      <c r="BV13" s="14"/>
-      <c r="BW13" s="12"/>
-      <c r="BX13" s="9"/>
-      <c r="BY13" s="10"/>
-      <c r="BZ13" s="11"/>
-      <c r="CA13" s="12"/>
-      <c r="CB13" s="9"/>
-      <c r="CC13" s="10"/>
-      <c r="CD13" s="11"/>
-      <c r="CE13" s="13"/>
-      <c r="CF13" s="14"/>
-      <c r="CG13" s="13"/>
-      <c r="CH13" s="14"/>
-      <c r="CI13" s="13"/>
-      <c r="CJ13" s="15"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="9"/>
+      <c r="AL13" s="10"/>
+      <c r="AM13" s="11"/>
+      <c r="AN13" s="13"/>
+      <c r="AO13" s="14"/>
+      <c r="AP13" s="13"/>
+      <c r="AQ13" s="14"/>
+      <c r="AR13" s="13"/>
+      <c r="AS13" s="15"/>
+      <c r="AT13" s="9"/>
+      <c r="AU13" s="10"/>
+      <c r="AV13" s="11"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="9"/>
+      <c r="AY13" s="10"/>
+      <c r="AZ13" s="11"/>
+      <c r="BA13" s="13"/>
+      <c r="BB13" s="14"/>
+      <c r="BC13" s="13"/>
+      <c r="BD13" s="14"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="9"/>
+      <c r="BG13" s="10"/>
+      <c r="BH13" s="11"/>
+      <c r="BI13" s="12"/>
+      <c r="BJ13" s="9"/>
+      <c r="BK13" s="10"/>
+      <c r="BL13" s="11"/>
+      <c r="BM13" s="13"/>
+      <c r="BN13" s="14"/>
+      <c r="BO13" s="13"/>
+      <c r="BP13" s="14"/>
+      <c r="BQ13" s="13"/>
+      <c r="BR13" s="15"/>
     </row>
-    <row r="14" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="10"/>
@@ -2725,69 +2398,51 @@
       <c r="AG14" s="11"/>
       <c r="AH14" s="13"/>
       <c r="AI14" s="14"/>
-      <c r="AJ14" s="13"/>
-      <c r="AK14" s="14"/>
-      <c r="AL14" s="13"/>
-      <c r="AM14" s="14"/>
-      <c r="AN14" s="12"/>
-      <c r="AO14" s="9"/>
-      <c r="AP14" s="10"/>
-      <c r="AQ14" s="11"/>
-      <c r="AR14" s="12"/>
-      <c r="AS14" s="9"/>
-      <c r="AT14" s="10"/>
-      <c r="AU14" s="11"/>
-      <c r="AV14" s="12"/>
-      <c r="AW14" s="9"/>
-      <c r="AX14" s="10"/>
-      <c r="AY14" s="11"/>
-      <c r="AZ14" s="13"/>
-      <c r="BA14" s="14"/>
-      <c r="BB14" s="12"/>
-      <c r="BC14" s="9"/>
-      <c r="BD14" s="10"/>
-      <c r="BE14" s="11"/>
-      <c r="BF14" s="13"/>
-      <c r="BG14" s="14"/>
-      <c r="BH14" s="13"/>
-      <c r="BI14" s="14"/>
-      <c r="BJ14" s="13"/>
-      <c r="BK14" s="15"/>
-      <c r="BL14" s="9"/>
-      <c r="BM14" s="10"/>
-      <c r="BN14" s="11"/>
-      <c r="BO14" s="12"/>
-      <c r="BP14" s="9"/>
-      <c r="BQ14" s="10"/>
-      <c r="BR14" s="11"/>
-      <c r="BS14" s="13"/>
-      <c r="BT14" s="14"/>
-      <c r="BU14" s="13"/>
-      <c r="BV14" s="14"/>
-      <c r="BW14" s="12"/>
-      <c r="BX14" s="9"/>
-      <c r="BY14" s="10"/>
-      <c r="BZ14" s="11"/>
-      <c r="CA14" s="12"/>
-      <c r="CB14" s="9"/>
-      <c r="CC14" s="10"/>
-      <c r="CD14" s="11"/>
-      <c r="CE14" s="13"/>
-      <c r="CF14" s="14"/>
-      <c r="CG14" s="13"/>
-      <c r="CH14" s="14"/>
-      <c r="CI14" s="13"/>
-      <c r="CJ14" s="15"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="9"/>
+      <c r="AL14" s="10"/>
+      <c r="AM14" s="11"/>
+      <c r="AN14" s="13"/>
+      <c r="AO14" s="14"/>
+      <c r="AP14" s="13"/>
+      <c r="AQ14" s="14"/>
+      <c r="AR14" s="13"/>
+      <c r="AS14" s="15"/>
+      <c r="AT14" s="9"/>
+      <c r="AU14" s="10"/>
+      <c r="AV14" s="11"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="9"/>
+      <c r="AY14" s="10"/>
+      <c r="AZ14" s="11"/>
+      <c r="BA14" s="13"/>
+      <c r="BB14" s="14"/>
+      <c r="BC14" s="13"/>
+      <c r="BD14" s="14"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="9"/>
+      <c r="BG14" s="10"/>
+      <c r="BH14" s="11"/>
+      <c r="BI14" s="12"/>
+      <c r="BJ14" s="9"/>
+      <c r="BK14" s="10"/>
+      <c r="BL14" s="11"/>
+      <c r="BM14" s="13"/>
+      <c r="BN14" s="14"/>
+      <c r="BO14" s="13"/>
+      <c r="BP14" s="14"/>
+      <c r="BQ14" s="13"/>
+      <c r="BR14" s="15"/>
     </row>
-    <row r="15" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="10"/>
@@ -2821,69 +2476,51 @@
       <c r="AG15" s="11"/>
       <c r="AH15" s="13"/>
       <c r="AI15" s="14"/>
-      <c r="AJ15" s="13"/>
-      <c r="AK15" s="14"/>
-      <c r="AL15" s="13"/>
-      <c r="AM15" s="14"/>
-      <c r="AN15" s="12"/>
-      <c r="AO15" s="9"/>
-      <c r="AP15" s="10"/>
-      <c r="AQ15" s="11"/>
-      <c r="AR15" s="12"/>
-      <c r="AS15" s="9"/>
-      <c r="AT15" s="10"/>
-      <c r="AU15" s="11"/>
-      <c r="AV15" s="12"/>
-      <c r="AW15" s="9"/>
-      <c r="AX15" s="10"/>
-      <c r="AY15" s="11"/>
-      <c r="AZ15" s="13"/>
-      <c r="BA15" s="14"/>
-      <c r="BB15" s="12"/>
-      <c r="BC15" s="9"/>
-      <c r="BD15" s="10"/>
-      <c r="BE15" s="11"/>
-      <c r="BF15" s="13"/>
-      <c r="BG15" s="14"/>
-      <c r="BH15" s="13"/>
-      <c r="BI15" s="14"/>
-      <c r="BJ15" s="13"/>
-      <c r="BK15" s="15"/>
-      <c r="BL15" s="9"/>
-      <c r="BM15" s="10"/>
-      <c r="BN15" s="11"/>
-      <c r="BO15" s="12"/>
-      <c r="BP15" s="9"/>
-      <c r="BQ15" s="10"/>
-      <c r="BR15" s="11"/>
-      <c r="BS15" s="13"/>
-      <c r="BT15" s="14"/>
-      <c r="BU15" s="13"/>
-      <c r="BV15" s="14"/>
-      <c r="BW15" s="12"/>
-      <c r="BX15" s="9"/>
-      <c r="BY15" s="10"/>
-      <c r="BZ15" s="11"/>
-      <c r="CA15" s="12"/>
-      <c r="CB15" s="9"/>
-      <c r="CC15" s="10"/>
-      <c r="CD15" s="11"/>
-      <c r="CE15" s="13"/>
-      <c r="CF15" s="14"/>
-      <c r="CG15" s="13"/>
-      <c r="CH15" s="14"/>
-      <c r="CI15" s="13"/>
-      <c r="CJ15" s="15"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="9"/>
+      <c r="AL15" s="10"/>
+      <c r="AM15" s="11"/>
+      <c r="AN15" s="13"/>
+      <c r="AO15" s="14"/>
+      <c r="AP15" s="13"/>
+      <c r="AQ15" s="14"/>
+      <c r="AR15" s="13"/>
+      <c r="AS15" s="15"/>
+      <c r="AT15" s="9"/>
+      <c r="AU15" s="10"/>
+      <c r="AV15" s="11"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="9"/>
+      <c r="AY15" s="10"/>
+      <c r="AZ15" s="11"/>
+      <c r="BA15" s="13"/>
+      <c r="BB15" s="14"/>
+      <c r="BC15" s="13"/>
+      <c r="BD15" s="14"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="9"/>
+      <c r="BG15" s="10"/>
+      <c r="BH15" s="11"/>
+      <c r="BI15" s="12"/>
+      <c r="BJ15" s="9"/>
+      <c r="BK15" s="10"/>
+      <c r="BL15" s="11"/>
+      <c r="BM15" s="13"/>
+      <c r="BN15" s="14"/>
+      <c r="BO15" s="13"/>
+      <c r="BP15" s="14"/>
+      <c r="BQ15" s="13"/>
+      <c r="BR15" s="15"/>
     </row>
-    <row r="16" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="10"/>
@@ -2917,69 +2554,51 @@
       <c r="AG16" s="11"/>
       <c r="AH16" s="13"/>
       <c r="AI16" s="14"/>
-      <c r="AJ16" s="13"/>
-      <c r="AK16" s="14"/>
-      <c r="AL16" s="13"/>
-      <c r="AM16" s="14"/>
-      <c r="AN16" s="12"/>
-      <c r="AO16" s="9"/>
-      <c r="AP16" s="10"/>
-      <c r="AQ16" s="11"/>
-      <c r="AR16" s="12"/>
-      <c r="AS16" s="9"/>
-      <c r="AT16" s="10"/>
-      <c r="AU16" s="11"/>
-      <c r="AV16" s="12"/>
-      <c r="AW16" s="9"/>
-      <c r="AX16" s="10"/>
-      <c r="AY16" s="11"/>
-      <c r="AZ16" s="13"/>
-      <c r="BA16" s="14"/>
-      <c r="BB16" s="12"/>
-      <c r="BC16" s="9"/>
-      <c r="BD16" s="10"/>
-      <c r="BE16" s="11"/>
-      <c r="BF16" s="13"/>
-      <c r="BG16" s="14"/>
-      <c r="BH16" s="13"/>
-      <c r="BI16" s="14"/>
-      <c r="BJ16" s="13"/>
-      <c r="BK16" s="15"/>
-      <c r="BL16" s="9"/>
-      <c r="BM16" s="10"/>
-      <c r="BN16" s="11"/>
-      <c r="BO16" s="12"/>
-      <c r="BP16" s="9"/>
-      <c r="BQ16" s="10"/>
-      <c r="BR16" s="11"/>
-      <c r="BS16" s="13"/>
-      <c r="BT16" s="14"/>
-      <c r="BU16" s="13"/>
-      <c r="BV16" s="14"/>
-      <c r="BW16" s="12"/>
-      <c r="BX16" s="9"/>
-      <c r="BY16" s="10"/>
-      <c r="BZ16" s="11"/>
-      <c r="CA16" s="12"/>
-      <c r="CB16" s="9"/>
-      <c r="CC16" s="10"/>
-      <c r="CD16" s="11"/>
-      <c r="CE16" s="13"/>
-      <c r="CF16" s="14"/>
-      <c r="CG16" s="13"/>
-      <c r="CH16" s="14"/>
-      <c r="CI16" s="13"/>
-      <c r="CJ16" s="15"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="9"/>
+      <c r="AL16" s="10"/>
+      <c r="AM16" s="11"/>
+      <c r="AN16" s="13"/>
+      <c r="AO16" s="14"/>
+      <c r="AP16" s="13"/>
+      <c r="AQ16" s="14"/>
+      <c r="AR16" s="13"/>
+      <c r="AS16" s="15"/>
+      <c r="AT16" s="9"/>
+      <c r="AU16" s="10"/>
+      <c r="AV16" s="11"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="9"/>
+      <c r="AY16" s="10"/>
+      <c r="AZ16" s="11"/>
+      <c r="BA16" s="13"/>
+      <c r="BB16" s="14"/>
+      <c r="BC16" s="13"/>
+      <c r="BD16" s="14"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="9"/>
+      <c r="BG16" s="10"/>
+      <c r="BH16" s="11"/>
+      <c r="BI16" s="12"/>
+      <c r="BJ16" s="9"/>
+      <c r="BK16" s="10"/>
+      <c r="BL16" s="11"/>
+      <c r="BM16" s="13"/>
+      <c r="BN16" s="14"/>
+      <c r="BO16" s="13"/>
+      <c r="BP16" s="14"/>
+      <c r="BQ16" s="13"/>
+      <c r="BR16" s="15"/>
     </row>
-    <row r="17" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="10"/>
@@ -3013,69 +2632,51 @@
       <c r="AG17" s="11"/>
       <c r="AH17" s="13"/>
       <c r="AI17" s="14"/>
-      <c r="AJ17" s="13"/>
-      <c r="AK17" s="14"/>
-      <c r="AL17" s="13"/>
-      <c r="AM17" s="14"/>
-      <c r="AN17" s="12"/>
-      <c r="AO17" s="9"/>
-      <c r="AP17" s="10"/>
-      <c r="AQ17" s="11"/>
-      <c r="AR17" s="12"/>
-      <c r="AS17" s="9"/>
-      <c r="AT17" s="10"/>
-      <c r="AU17" s="11"/>
-      <c r="AV17" s="12"/>
-      <c r="AW17" s="9"/>
-      <c r="AX17" s="10"/>
-      <c r="AY17" s="11"/>
-      <c r="AZ17" s="13"/>
-      <c r="BA17" s="14"/>
-      <c r="BB17" s="12"/>
-      <c r="BC17" s="9"/>
-      <c r="BD17" s="10"/>
-      <c r="BE17" s="11"/>
-      <c r="BF17" s="13"/>
-      <c r="BG17" s="14"/>
-      <c r="BH17" s="13"/>
-      <c r="BI17" s="14"/>
-      <c r="BJ17" s="13"/>
-      <c r="BK17" s="15"/>
-      <c r="BL17" s="9"/>
-      <c r="BM17" s="10"/>
-      <c r="BN17" s="11"/>
-      <c r="BO17" s="12"/>
-      <c r="BP17" s="9"/>
-      <c r="BQ17" s="10"/>
-      <c r="BR17" s="11"/>
-      <c r="BS17" s="13"/>
-      <c r="BT17" s="14"/>
-      <c r="BU17" s="13"/>
-      <c r="BV17" s="14"/>
-      <c r="BW17" s="12"/>
-      <c r="BX17" s="9"/>
-      <c r="BY17" s="10"/>
-      <c r="BZ17" s="11"/>
-      <c r="CA17" s="12"/>
-      <c r="CB17" s="9"/>
-      <c r="CC17" s="10"/>
-      <c r="CD17" s="11"/>
-      <c r="CE17" s="13"/>
-      <c r="CF17" s="14"/>
-      <c r="CG17" s="13"/>
-      <c r="CH17" s="14"/>
-      <c r="CI17" s="13"/>
-      <c r="CJ17" s="15"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="9"/>
+      <c r="AL17" s="10"/>
+      <c r="AM17" s="11"/>
+      <c r="AN17" s="13"/>
+      <c r="AO17" s="14"/>
+      <c r="AP17" s="13"/>
+      <c r="AQ17" s="14"/>
+      <c r="AR17" s="13"/>
+      <c r="AS17" s="15"/>
+      <c r="AT17" s="9"/>
+      <c r="AU17" s="10"/>
+      <c r="AV17" s="11"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="9"/>
+      <c r="AY17" s="10"/>
+      <c r="AZ17" s="11"/>
+      <c r="BA17" s="13"/>
+      <c r="BB17" s="14"/>
+      <c r="BC17" s="13"/>
+      <c r="BD17" s="14"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="9"/>
+      <c r="BG17" s="10"/>
+      <c r="BH17" s="11"/>
+      <c r="BI17" s="12"/>
+      <c r="BJ17" s="9"/>
+      <c r="BK17" s="10"/>
+      <c r="BL17" s="11"/>
+      <c r="BM17" s="13"/>
+      <c r="BN17" s="14"/>
+      <c r="BO17" s="13"/>
+      <c r="BP17" s="14"/>
+      <c r="BQ17" s="13"/>
+      <c r="BR17" s="15"/>
     </row>
-    <row r="18" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="10"/>
@@ -3109,69 +2710,51 @@
       <c r="AG18" s="11"/>
       <c r="AH18" s="13"/>
       <c r="AI18" s="14"/>
-      <c r="AJ18" s="13"/>
-      <c r="AK18" s="14"/>
-      <c r="AL18" s="13"/>
-      <c r="AM18" s="14"/>
-      <c r="AN18" s="12"/>
-      <c r="AO18" s="9"/>
-      <c r="AP18" s="10"/>
-      <c r="AQ18" s="11"/>
-      <c r="AR18" s="12"/>
-      <c r="AS18" s="9"/>
-      <c r="AT18" s="10"/>
-      <c r="AU18" s="11"/>
-      <c r="AV18" s="12"/>
-      <c r="AW18" s="9"/>
-      <c r="AX18" s="10"/>
-      <c r="AY18" s="11"/>
-      <c r="AZ18" s="13"/>
-      <c r="BA18" s="14"/>
-      <c r="BB18" s="12"/>
-      <c r="BC18" s="9"/>
-      <c r="BD18" s="10"/>
-      <c r="BE18" s="11"/>
-      <c r="BF18" s="13"/>
-      <c r="BG18" s="14"/>
-      <c r="BH18" s="13"/>
-      <c r="BI18" s="14"/>
-      <c r="BJ18" s="13"/>
-      <c r="BK18" s="15"/>
-      <c r="BL18" s="9"/>
-      <c r="BM18" s="10"/>
-      <c r="BN18" s="11"/>
-      <c r="BO18" s="12"/>
-      <c r="BP18" s="9"/>
-      <c r="BQ18" s="10"/>
-      <c r="BR18" s="11"/>
-      <c r="BS18" s="13"/>
-      <c r="BT18" s="14"/>
-      <c r="BU18" s="13"/>
-      <c r="BV18" s="14"/>
-      <c r="BW18" s="12"/>
-      <c r="BX18" s="9"/>
-      <c r="BY18" s="10"/>
-      <c r="BZ18" s="11"/>
-      <c r="CA18" s="12"/>
-      <c r="CB18" s="9"/>
-      <c r="CC18" s="10"/>
-      <c r="CD18" s="11"/>
-      <c r="CE18" s="13"/>
-      <c r="CF18" s="14"/>
-      <c r="CG18" s="13"/>
-      <c r="CH18" s="14"/>
-      <c r="CI18" s="13"/>
-      <c r="CJ18" s="15"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="9"/>
+      <c r="AL18" s="10"/>
+      <c r="AM18" s="11"/>
+      <c r="AN18" s="13"/>
+      <c r="AO18" s="14"/>
+      <c r="AP18" s="13"/>
+      <c r="AQ18" s="14"/>
+      <c r="AR18" s="13"/>
+      <c r="AS18" s="15"/>
+      <c r="AT18" s="9"/>
+      <c r="AU18" s="10"/>
+      <c r="AV18" s="11"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="9"/>
+      <c r="AY18" s="10"/>
+      <c r="AZ18" s="11"/>
+      <c r="BA18" s="13"/>
+      <c r="BB18" s="14"/>
+      <c r="BC18" s="13"/>
+      <c r="BD18" s="14"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="9"/>
+      <c r="BG18" s="10"/>
+      <c r="BH18" s="11"/>
+      <c r="BI18" s="12"/>
+      <c r="BJ18" s="9"/>
+      <c r="BK18" s="10"/>
+      <c r="BL18" s="11"/>
+      <c r="BM18" s="13"/>
+      <c r="BN18" s="14"/>
+      <c r="BO18" s="13"/>
+      <c r="BP18" s="14"/>
+      <c r="BQ18" s="13"/>
+      <c r="BR18" s="15"/>
     </row>
-    <row r="19" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="10"/>
@@ -3205,69 +2788,51 @@
       <c r="AG19" s="11"/>
       <c r="AH19" s="13"/>
       <c r="AI19" s="14"/>
-      <c r="AJ19" s="13"/>
-      <c r="AK19" s="14"/>
-      <c r="AL19" s="13"/>
-      <c r="AM19" s="14"/>
-      <c r="AN19" s="12"/>
-      <c r="AO19" s="9"/>
-      <c r="AP19" s="10"/>
-      <c r="AQ19" s="11"/>
-      <c r="AR19" s="12"/>
-      <c r="AS19" s="9"/>
-      <c r="AT19" s="10"/>
-      <c r="AU19" s="11"/>
-      <c r="AV19" s="12"/>
-      <c r="AW19" s="9"/>
-      <c r="AX19" s="10"/>
-      <c r="AY19" s="11"/>
-      <c r="AZ19" s="13"/>
-      <c r="BA19" s="14"/>
-      <c r="BB19" s="12"/>
-      <c r="BC19" s="9"/>
-      <c r="BD19" s="10"/>
-      <c r="BE19" s="11"/>
-      <c r="BF19" s="13"/>
-      <c r="BG19" s="14"/>
-      <c r="BH19" s="13"/>
-      <c r="BI19" s="14"/>
-      <c r="BJ19" s="13"/>
-      <c r="BK19" s="15"/>
-      <c r="BL19" s="9"/>
-      <c r="BM19" s="10"/>
-      <c r="BN19" s="11"/>
-      <c r="BO19" s="12"/>
-      <c r="BP19" s="9"/>
-      <c r="BQ19" s="10"/>
-      <c r="BR19" s="11"/>
-      <c r="BS19" s="13"/>
-      <c r="BT19" s="14"/>
-      <c r="BU19" s="13"/>
-      <c r="BV19" s="14"/>
-      <c r="BW19" s="12"/>
-      <c r="BX19" s="9"/>
-      <c r="BY19" s="10"/>
-      <c r="BZ19" s="11"/>
-      <c r="CA19" s="12"/>
-      <c r="CB19" s="9"/>
-      <c r="CC19" s="10"/>
-      <c r="CD19" s="11"/>
-      <c r="CE19" s="13"/>
-      <c r="CF19" s="14"/>
-      <c r="CG19" s="13"/>
-      <c r="CH19" s="14"/>
-      <c r="CI19" s="13"/>
-      <c r="CJ19" s="15"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="9"/>
+      <c r="AL19" s="10"/>
+      <c r="AM19" s="11"/>
+      <c r="AN19" s="13"/>
+      <c r="AO19" s="14"/>
+      <c r="AP19" s="13"/>
+      <c r="AQ19" s="14"/>
+      <c r="AR19" s="13"/>
+      <c r="AS19" s="15"/>
+      <c r="AT19" s="9"/>
+      <c r="AU19" s="10"/>
+      <c r="AV19" s="11"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="9"/>
+      <c r="AY19" s="10"/>
+      <c r="AZ19" s="11"/>
+      <c r="BA19" s="13"/>
+      <c r="BB19" s="14"/>
+      <c r="BC19" s="13"/>
+      <c r="BD19" s="14"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="9"/>
+      <c r="BG19" s="10"/>
+      <c r="BH19" s="11"/>
+      <c r="BI19" s="12"/>
+      <c r="BJ19" s="9"/>
+      <c r="BK19" s="10"/>
+      <c r="BL19" s="11"/>
+      <c r="BM19" s="13"/>
+      <c r="BN19" s="14"/>
+      <c r="BO19" s="13"/>
+      <c r="BP19" s="14"/>
+      <c r="BQ19" s="13"/>
+      <c r="BR19" s="15"/>
     </row>
-    <row r="20" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="10"/>
@@ -3301,69 +2866,51 @@
       <c r="AG20" s="11"/>
       <c r="AH20" s="13"/>
       <c r="AI20" s="14"/>
-      <c r="AJ20" s="13"/>
-      <c r="AK20" s="14"/>
-      <c r="AL20" s="13"/>
-      <c r="AM20" s="14"/>
-      <c r="AN20" s="12"/>
-      <c r="AO20" s="9"/>
-      <c r="AP20" s="10"/>
-      <c r="AQ20" s="11"/>
-      <c r="AR20" s="12"/>
-      <c r="AS20" s="9"/>
-      <c r="AT20" s="10"/>
-      <c r="AU20" s="11"/>
-      <c r="AV20" s="12"/>
-      <c r="AW20" s="9"/>
-      <c r="AX20" s="10"/>
-      <c r="AY20" s="11"/>
-      <c r="AZ20" s="13"/>
-      <c r="BA20" s="14"/>
-      <c r="BB20" s="12"/>
-      <c r="BC20" s="9"/>
-      <c r="BD20" s="10"/>
-      <c r="BE20" s="11"/>
-      <c r="BF20" s="13"/>
-      <c r="BG20" s="14"/>
-      <c r="BH20" s="13"/>
-      <c r="BI20" s="14"/>
-      <c r="BJ20" s="13"/>
-      <c r="BK20" s="15"/>
-      <c r="BL20" s="9"/>
-      <c r="BM20" s="10"/>
-      <c r="BN20" s="11"/>
-      <c r="BO20" s="12"/>
-      <c r="BP20" s="9"/>
-      <c r="BQ20" s="10"/>
-      <c r="BR20" s="11"/>
-      <c r="BS20" s="13"/>
-      <c r="BT20" s="14"/>
-      <c r="BU20" s="13"/>
-      <c r="BV20" s="14"/>
-      <c r="BW20" s="12"/>
-      <c r="BX20" s="9"/>
-      <c r="BY20" s="10"/>
-      <c r="BZ20" s="11"/>
-      <c r="CA20" s="12"/>
-      <c r="CB20" s="9"/>
-      <c r="CC20" s="10"/>
-      <c r="CD20" s="11"/>
-      <c r="CE20" s="13"/>
-      <c r="CF20" s="14"/>
-      <c r="CG20" s="13"/>
-      <c r="CH20" s="14"/>
-      <c r="CI20" s="13"/>
-      <c r="CJ20" s="15"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="9"/>
+      <c r="AL20" s="10"/>
+      <c r="AM20" s="11"/>
+      <c r="AN20" s="13"/>
+      <c r="AO20" s="14"/>
+      <c r="AP20" s="13"/>
+      <c r="AQ20" s="14"/>
+      <c r="AR20" s="13"/>
+      <c r="AS20" s="15"/>
+      <c r="AT20" s="9"/>
+      <c r="AU20" s="10"/>
+      <c r="AV20" s="11"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="9"/>
+      <c r="AY20" s="10"/>
+      <c r="AZ20" s="11"/>
+      <c r="BA20" s="13"/>
+      <c r="BB20" s="14"/>
+      <c r="BC20" s="13"/>
+      <c r="BD20" s="14"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="9"/>
+      <c r="BG20" s="10"/>
+      <c r="BH20" s="11"/>
+      <c r="BI20" s="12"/>
+      <c r="BJ20" s="9"/>
+      <c r="BK20" s="10"/>
+      <c r="BL20" s="11"/>
+      <c r="BM20" s="13"/>
+      <c r="BN20" s="14"/>
+      <c r="BO20" s="13"/>
+      <c r="BP20" s="14"/>
+      <c r="BQ20" s="13"/>
+      <c r="BR20" s="15"/>
     </row>
-    <row r="21" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="10"/>
@@ -3397,69 +2944,51 @@
       <c r="AG21" s="11"/>
       <c r="AH21" s="13"/>
       <c r="AI21" s="14"/>
-      <c r="AJ21" s="13"/>
-      <c r="AK21" s="14"/>
-      <c r="AL21" s="13"/>
-      <c r="AM21" s="14"/>
-      <c r="AN21" s="12"/>
-      <c r="AO21" s="9"/>
-      <c r="AP21" s="10"/>
-      <c r="AQ21" s="11"/>
-      <c r="AR21" s="12"/>
-      <c r="AS21" s="9"/>
-      <c r="AT21" s="10"/>
-      <c r="AU21" s="11"/>
-      <c r="AV21" s="12"/>
-      <c r="AW21" s="9"/>
-      <c r="AX21" s="10"/>
-      <c r="AY21" s="11"/>
-      <c r="AZ21" s="13"/>
-      <c r="BA21" s="14"/>
-      <c r="BB21" s="12"/>
-      <c r="BC21" s="9"/>
-      <c r="BD21" s="10"/>
-      <c r="BE21" s="11"/>
-      <c r="BF21" s="13"/>
-      <c r="BG21" s="14"/>
-      <c r="BH21" s="13"/>
-      <c r="BI21" s="14"/>
-      <c r="BJ21" s="13"/>
-      <c r="BK21" s="15"/>
-      <c r="BL21" s="9"/>
-      <c r="BM21" s="10"/>
-      <c r="BN21" s="11"/>
-      <c r="BO21" s="12"/>
-      <c r="BP21" s="9"/>
-      <c r="BQ21" s="10"/>
-      <c r="BR21" s="11"/>
-      <c r="BS21" s="13"/>
-      <c r="BT21" s="14"/>
-      <c r="BU21" s="13"/>
-      <c r="BV21" s="14"/>
-      <c r="BW21" s="12"/>
-      <c r="BX21" s="9"/>
-      <c r="BY21" s="10"/>
-      <c r="BZ21" s="11"/>
-      <c r="CA21" s="12"/>
-      <c r="CB21" s="9"/>
-      <c r="CC21" s="10"/>
-      <c r="CD21" s="11"/>
-      <c r="CE21" s="13"/>
-      <c r="CF21" s="14"/>
-      <c r="CG21" s="13"/>
-      <c r="CH21" s="14"/>
-      <c r="CI21" s="13"/>
-      <c r="CJ21" s="15"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="9"/>
+      <c r="AL21" s="10"/>
+      <c r="AM21" s="11"/>
+      <c r="AN21" s="13"/>
+      <c r="AO21" s="14"/>
+      <c r="AP21" s="13"/>
+      <c r="AQ21" s="14"/>
+      <c r="AR21" s="13"/>
+      <c r="AS21" s="15"/>
+      <c r="AT21" s="9"/>
+      <c r="AU21" s="10"/>
+      <c r="AV21" s="11"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="9"/>
+      <c r="AY21" s="10"/>
+      <c r="AZ21" s="11"/>
+      <c r="BA21" s="13"/>
+      <c r="BB21" s="14"/>
+      <c r="BC21" s="13"/>
+      <c r="BD21" s="14"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="9"/>
+      <c r="BG21" s="10"/>
+      <c r="BH21" s="11"/>
+      <c r="BI21" s="12"/>
+      <c r="BJ21" s="9"/>
+      <c r="BK21" s="10"/>
+      <c r="BL21" s="11"/>
+      <c r="BM21" s="13"/>
+      <c r="BN21" s="14"/>
+      <c r="BO21" s="13"/>
+      <c r="BP21" s="14"/>
+      <c r="BQ21" s="13"/>
+      <c r="BR21" s="15"/>
     </row>
-    <row r="22" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="10"/>
@@ -3493,69 +3022,51 @@
       <c r="AG22" s="11"/>
       <c r="AH22" s="13"/>
       <c r="AI22" s="14"/>
-      <c r="AJ22" s="13"/>
-      <c r="AK22" s="14"/>
-      <c r="AL22" s="13"/>
-      <c r="AM22" s="14"/>
-      <c r="AN22" s="12"/>
-      <c r="AO22" s="9"/>
-      <c r="AP22" s="10"/>
-      <c r="AQ22" s="11"/>
-      <c r="AR22" s="12"/>
-      <c r="AS22" s="9"/>
-      <c r="AT22" s="10"/>
-      <c r="AU22" s="11"/>
-      <c r="AV22" s="12"/>
-      <c r="AW22" s="9"/>
-      <c r="AX22" s="10"/>
-      <c r="AY22" s="11"/>
-      <c r="AZ22" s="13"/>
-      <c r="BA22" s="14"/>
-      <c r="BB22" s="12"/>
-      <c r="BC22" s="9"/>
-      <c r="BD22" s="10"/>
-      <c r="BE22" s="11"/>
-      <c r="BF22" s="13"/>
-      <c r="BG22" s="14"/>
-      <c r="BH22" s="13"/>
-      <c r="BI22" s="14"/>
-      <c r="BJ22" s="13"/>
-      <c r="BK22" s="15"/>
-      <c r="BL22" s="9"/>
-      <c r="BM22" s="10"/>
-      <c r="BN22" s="11"/>
-      <c r="BO22" s="12"/>
-      <c r="BP22" s="9"/>
-      <c r="BQ22" s="10"/>
-      <c r="BR22" s="11"/>
-      <c r="BS22" s="13"/>
-      <c r="BT22" s="14"/>
-      <c r="BU22" s="13"/>
-      <c r="BV22" s="14"/>
-      <c r="BW22" s="12"/>
-      <c r="BX22" s="9"/>
-      <c r="BY22" s="10"/>
-      <c r="BZ22" s="11"/>
-      <c r="CA22" s="12"/>
-      <c r="CB22" s="9"/>
-      <c r="CC22" s="10"/>
-      <c r="CD22" s="11"/>
-      <c r="CE22" s="13"/>
-      <c r="CF22" s="14"/>
-      <c r="CG22" s="13"/>
-      <c r="CH22" s="14"/>
-      <c r="CI22" s="13"/>
-      <c r="CJ22" s="15"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="9"/>
+      <c r="AL22" s="10"/>
+      <c r="AM22" s="11"/>
+      <c r="AN22" s="13"/>
+      <c r="AO22" s="14"/>
+      <c r="AP22" s="13"/>
+      <c r="AQ22" s="14"/>
+      <c r="AR22" s="13"/>
+      <c r="AS22" s="15"/>
+      <c r="AT22" s="9"/>
+      <c r="AU22" s="10"/>
+      <c r="AV22" s="11"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="9"/>
+      <c r="AY22" s="10"/>
+      <c r="AZ22" s="11"/>
+      <c r="BA22" s="13"/>
+      <c r="BB22" s="14"/>
+      <c r="BC22" s="13"/>
+      <c r="BD22" s="14"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="9"/>
+      <c r="BG22" s="10"/>
+      <c r="BH22" s="11"/>
+      <c r="BI22" s="12"/>
+      <c r="BJ22" s="9"/>
+      <c r="BK22" s="10"/>
+      <c r="BL22" s="11"/>
+      <c r="BM22" s="13"/>
+      <c r="BN22" s="14"/>
+      <c r="BO22" s="13"/>
+      <c r="BP22" s="14"/>
+      <c r="BQ22" s="13"/>
+      <c r="BR22" s="15"/>
     </row>
-    <row r="23" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="10"/>
@@ -3589,69 +3100,51 @@
       <c r="AG23" s="11"/>
       <c r="AH23" s="13"/>
       <c r="AI23" s="14"/>
-      <c r="AJ23" s="13"/>
-      <c r="AK23" s="14"/>
-      <c r="AL23" s="13"/>
-      <c r="AM23" s="14"/>
-      <c r="AN23" s="12"/>
-      <c r="AO23" s="9"/>
-      <c r="AP23" s="10"/>
-      <c r="AQ23" s="11"/>
-      <c r="AR23" s="12"/>
-      <c r="AS23" s="9"/>
-      <c r="AT23" s="10"/>
-      <c r="AU23" s="11"/>
-      <c r="AV23" s="12"/>
-      <c r="AW23" s="9"/>
-      <c r="AX23" s="10"/>
-      <c r="AY23" s="11"/>
-      <c r="AZ23" s="13"/>
-      <c r="BA23" s="14"/>
-      <c r="BB23" s="12"/>
-      <c r="BC23" s="9"/>
-      <c r="BD23" s="10"/>
-      <c r="BE23" s="11"/>
-      <c r="BF23" s="13"/>
-      <c r="BG23" s="14"/>
-      <c r="BH23" s="13"/>
-      <c r="BI23" s="14"/>
-      <c r="BJ23" s="13"/>
-      <c r="BK23" s="15"/>
-      <c r="BL23" s="9"/>
-      <c r="BM23" s="10"/>
-      <c r="BN23" s="11"/>
-      <c r="BO23" s="12"/>
-      <c r="BP23" s="9"/>
-      <c r="BQ23" s="10"/>
-      <c r="BR23" s="11"/>
-      <c r="BS23" s="13"/>
-      <c r="BT23" s="14"/>
-      <c r="BU23" s="13"/>
-      <c r="BV23" s="14"/>
-      <c r="BW23" s="12"/>
-      <c r="BX23" s="9"/>
-      <c r="BY23" s="10"/>
-      <c r="BZ23" s="11"/>
-      <c r="CA23" s="12"/>
-      <c r="CB23" s="9"/>
-      <c r="CC23" s="10"/>
-      <c r="CD23" s="11"/>
-      <c r="CE23" s="13"/>
-      <c r="CF23" s="14"/>
-      <c r="CG23" s="13"/>
-      <c r="CH23" s="14"/>
-      <c r="CI23" s="13"/>
-      <c r="CJ23" s="15"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="9"/>
+      <c r="AL23" s="10"/>
+      <c r="AM23" s="11"/>
+      <c r="AN23" s="13"/>
+      <c r="AO23" s="14"/>
+      <c r="AP23" s="13"/>
+      <c r="AQ23" s="14"/>
+      <c r="AR23" s="13"/>
+      <c r="AS23" s="15"/>
+      <c r="AT23" s="9"/>
+      <c r="AU23" s="10"/>
+      <c r="AV23" s="11"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="9"/>
+      <c r="AY23" s="10"/>
+      <c r="AZ23" s="11"/>
+      <c r="BA23" s="13"/>
+      <c r="BB23" s="14"/>
+      <c r="BC23" s="13"/>
+      <c r="BD23" s="14"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="9"/>
+      <c r="BG23" s="10"/>
+      <c r="BH23" s="11"/>
+      <c r="BI23" s="12"/>
+      <c r="BJ23" s="9"/>
+      <c r="BK23" s="10"/>
+      <c r="BL23" s="11"/>
+      <c r="BM23" s="13"/>
+      <c r="BN23" s="14"/>
+      <c r="BO23" s="13"/>
+      <c r="BP23" s="14"/>
+      <c r="BQ23" s="13"/>
+      <c r="BR23" s="15"/>
     </row>
-    <row r="24" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="10"/>
@@ -3685,69 +3178,51 @@
       <c r="AG24" s="11"/>
       <c r="AH24" s="13"/>
       <c r="AI24" s="14"/>
-      <c r="AJ24" s="13"/>
-      <c r="AK24" s="14"/>
-      <c r="AL24" s="13"/>
-      <c r="AM24" s="14"/>
-      <c r="AN24" s="12"/>
-      <c r="AO24" s="9"/>
-      <c r="AP24" s="10"/>
-      <c r="AQ24" s="11"/>
-      <c r="AR24" s="12"/>
-      <c r="AS24" s="9"/>
-      <c r="AT24" s="10"/>
-      <c r="AU24" s="11"/>
-      <c r="AV24" s="12"/>
-      <c r="AW24" s="9"/>
-      <c r="AX24" s="10"/>
-      <c r="AY24" s="11"/>
-      <c r="AZ24" s="13"/>
-      <c r="BA24" s="14"/>
-      <c r="BB24" s="12"/>
-      <c r="BC24" s="9"/>
-      <c r="BD24" s="10"/>
-      <c r="BE24" s="11"/>
-      <c r="BF24" s="13"/>
-      <c r="BG24" s="14"/>
-      <c r="BH24" s="13"/>
-      <c r="BI24" s="14"/>
-      <c r="BJ24" s="13"/>
-      <c r="BK24" s="15"/>
-      <c r="BL24" s="9"/>
-      <c r="BM24" s="10"/>
-      <c r="BN24" s="11"/>
-      <c r="BO24" s="12"/>
-      <c r="BP24" s="9"/>
-      <c r="BQ24" s="10"/>
-      <c r="BR24" s="11"/>
-      <c r="BS24" s="13"/>
-      <c r="BT24" s="14"/>
-      <c r="BU24" s="13"/>
-      <c r="BV24" s="14"/>
-      <c r="BW24" s="12"/>
-      <c r="BX24" s="9"/>
-      <c r="BY24" s="10"/>
-      <c r="BZ24" s="11"/>
-      <c r="CA24" s="12"/>
-      <c r="CB24" s="9"/>
-      <c r="CC24" s="10"/>
-      <c r="CD24" s="11"/>
-      <c r="CE24" s="13"/>
-      <c r="CF24" s="14"/>
-      <c r="CG24" s="13"/>
-      <c r="CH24" s="14"/>
-      <c r="CI24" s="13"/>
-      <c r="CJ24" s="15"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="9"/>
+      <c r="AL24" s="10"/>
+      <c r="AM24" s="11"/>
+      <c r="AN24" s="13"/>
+      <c r="AO24" s="14"/>
+      <c r="AP24" s="13"/>
+      <c r="AQ24" s="14"/>
+      <c r="AR24" s="13"/>
+      <c r="AS24" s="15"/>
+      <c r="AT24" s="9"/>
+      <c r="AU24" s="10"/>
+      <c r="AV24" s="11"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="9"/>
+      <c r="AY24" s="10"/>
+      <c r="AZ24" s="11"/>
+      <c r="BA24" s="13"/>
+      <c r="BB24" s="14"/>
+      <c r="BC24" s="13"/>
+      <c r="BD24" s="14"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="9"/>
+      <c r="BG24" s="10"/>
+      <c r="BH24" s="11"/>
+      <c r="BI24" s="12"/>
+      <c r="BJ24" s="9"/>
+      <c r="BK24" s="10"/>
+      <c r="BL24" s="11"/>
+      <c r="BM24" s="13"/>
+      <c r="BN24" s="14"/>
+      <c r="BO24" s="13"/>
+      <c r="BP24" s="14"/>
+      <c r="BQ24" s="13"/>
+      <c r="BR24" s="15"/>
     </row>
-    <row r="25" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="10"/>
@@ -3781,69 +3256,51 @@
       <c r="AG25" s="11"/>
       <c r="AH25" s="13"/>
       <c r="AI25" s="14"/>
-      <c r="AJ25" s="13"/>
-      <c r="AK25" s="14"/>
-      <c r="AL25" s="13"/>
-      <c r="AM25" s="14"/>
-      <c r="AN25" s="12"/>
-      <c r="AO25" s="9"/>
-      <c r="AP25" s="10"/>
-      <c r="AQ25" s="11"/>
-      <c r="AR25" s="12"/>
-      <c r="AS25" s="9"/>
-      <c r="AT25" s="10"/>
-      <c r="AU25" s="11"/>
-      <c r="AV25" s="12"/>
-      <c r="AW25" s="9"/>
-      <c r="AX25" s="10"/>
-      <c r="AY25" s="11"/>
-      <c r="AZ25" s="13"/>
-      <c r="BA25" s="14"/>
-      <c r="BB25" s="12"/>
-      <c r="BC25" s="9"/>
-      <c r="BD25" s="10"/>
-      <c r="BE25" s="11"/>
-      <c r="BF25" s="13"/>
-      <c r="BG25" s="14"/>
-      <c r="BH25" s="13"/>
-      <c r="BI25" s="14"/>
-      <c r="BJ25" s="13"/>
-      <c r="BK25" s="15"/>
-      <c r="BL25" s="9"/>
-      <c r="BM25" s="10"/>
-      <c r="BN25" s="11"/>
-      <c r="BO25" s="12"/>
-      <c r="BP25" s="9"/>
-      <c r="BQ25" s="10"/>
-      <c r="BR25" s="11"/>
-      <c r="BS25" s="13"/>
-      <c r="BT25" s="14"/>
-      <c r="BU25" s="13"/>
-      <c r="BV25" s="14"/>
-      <c r="BW25" s="12"/>
-      <c r="BX25" s="9"/>
-      <c r="BY25" s="10"/>
-      <c r="BZ25" s="11"/>
-      <c r="CA25" s="12"/>
-      <c r="CB25" s="9"/>
-      <c r="CC25" s="10"/>
-      <c r="CD25" s="11"/>
-      <c r="CE25" s="13"/>
-      <c r="CF25" s="14"/>
-      <c r="CG25" s="13"/>
-      <c r="CH25" s="14"/>
-      <c r="CI25" s="13"/>
-      <c r="CJ25" s="15"/>
+      <c r="AJ25" s="12"/>
+      <c r="AK25" s="9"/>
+      <c r="AL25" s="10"/>
+      <c r="AM25" s="11"/>
+      <c r="AN25" s="13"/>
+      <c r="AO25" s="14"/>
+      <c r="AP25" s="13"/>
+      <c r="AQ25" s="14"/>
+      <c r="AR25" s="13"/>
+      <c r="AS25" s="15"/>
+      <c r="AT25" s="9"/>
+      <c r="AU25" s="10"/>
+      <c r="AV25" s="11"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="9"/>
+      <c r="AY25" s="10"/>
+      <c r="AZ25" s="11"/>
+      <c r="BA25" s="13"/>
+      <c r="BB25" s="14"/>
+      <c r="BC25" s="13"/>
+      <c r="BD25" s="14"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="9"/>
+      <c r="BG25" s="10"/>
+      <c r="BH25" s="11"/>
+      <c r="BI25" s="12"/>
+      <c r="BJ25" s="9"/>
+      <c r="BK25" s="10"/>
+      <c r="BL25" s="11"/>
+      <c r="BM25" s="13"/>
+      <c r="BN25" s="14"/>
+      <c r="BO25" s="13"/>
+      <c r="BP25" s="14"/>
+      <c r="BQ25" s="13"/>
+      <c r="BR25" s="15"/>
     </row>
-    <row r="26" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="10"/>
@@ -3877,69 +3334,51 @@
       <c r="AG26" s="11"/>
       <c r="AH26" s="13"/>
       <c r="AI26" s="14"/>
-      <c r="AJ26" s="13"/>
-      <c r="AK26" s="14"/>
-      <c r="AL26" s="13"/>
-      <c r="AM26" s="14"/>
-      <c r="AN26" s="12"/>
-      <c r="AO26" s="9"/>
-      <c r="AP26" s="10"/>
-      <c r="AQ26" s="11"/>
-      <c r="AR26" s="12"/>
-      <c r="AS26" s="9"/>
-      <c r="AT26" s="10"/>
-      <c r="AU26" s="11"/>
-      <c r="AV26" s="12"/>
-      <c r="AW26" s="9"/>
-      <c r="AX26" s="10"/>
-      <c r="AY26" s="11"/>
-      <c r="AZ26" s="13"/>
-      <c r="BA26" s="14"/>
-      <c r="BB26" s="12"/>
-      <c r="BC26" s="9"/>
-      <c r="BD26" s="10"/>
-      <c r="BE26" s="11"/>
-      <c r="BF26" s="13"/>
-      <c r="BG26" s="14"/>
-      <c r="BH26" s="13"/>
-      <c r="BI26" s="14"/>
-      <c r="BJ26" s="13"/>
-      <c r="BK26" s="15"/>
-      <c r="BL26" s="9"/>
-      <c r="BM26" s="10"/>
-      <c r="BN26" s="11"/>
-      <c r="BO26" s="12"/>
-      <c r="BP26" s="9"/>
-      <c r="BQ26" s="10"/>
-      <c r="BR26" s="11"/>
-      <c r="BS26" s="13"/>
-      <c r="BT26" s="14"/>
-      <c r="BU26" s="13"/>
-      <c r="BV26" s="14"/>
-      <c r="BW26" s="12"/>
-      <c r="BX26" s="9"/>
-      <c r="BY26" s="10"/>
-      <c r="BZ26" s="11"/>
-      <c r="CA26" s="12"/>
-      <c r="CB26" s="9"/>
-      <c r="CC26" s="10"/>
-      <c r="CD26" s="11"/>
-      <c r="CE26" s="13"/>
-      <c r="CF26" s="14"/>
-      <c r="CG26" s="13"/>
-      <c r="CH26" s="14"/>
-      <c r="CI26" s="13"/>
-      <c r="CJ26" s="15"/>
+      <c r="AJ26" s="12"/>
+      <c r="AK26" s="9"/>
+      <c r="AL26" s="10"/>
+      <c r="AM26" s="11"/>
+      <c r="AN26" s="13"/>
+      <c r="AO26" s="14"/>
+      <c r="AP26" s="13"/>
+      <c r="AQ26" s="14"/>
+      <c r="AR26" s="13"/>
+      <c r="AS26" s="15"/>
+      <c r="AT26" s="9"/>
+      <c r="AU26" s="10"/>
+      <c r="AV26" s="11"/>
+      <c r="AW26" s="12"/>
+      <c r="AX26" s="9"/>
+      <c r="AY26" s="10"/>
+      <c r="AZ26" s="11"/>
+      <c r="BA26" s="13"/>
+      <c r="BB26" s="14"/>
+      <c r="BC26" s="13"/>
+      <c r="BD26" s="14"/>
+      <c r="BE26" s="12"/>
+      <c r="BF26" s="9"/>
+      <c r="BG26" s="10"/>
+      <c r="BH26" s="11"/>
+      <c r="BI26" s="12"/>
+      <c r="BJ26" s="9"/>
+      <c r="BK26" s="10"/>
+      <c r="BL26" s="11"/>
+      <c r="BM26" s="13"/>
+      <c r="BN26" s="14"/>
+      <c r="BO26" s="13"/>
+      <c r="BP26" s="14"/>
+      <c r="BQ26" s="13"/>
+      <c r="BR26" s="15"/>
     </row>
-    <row r="27" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="10"/>
@@ -3973,67 +3412,49 @@
       <c r="AG27" s="11"/>
       <c r="AH27" s="13"/>
       <c r="AI27" s="14"/>
-      <c r="AJ27" s="13"/>
-      <c r="AK27" s="14"/>
-      <c r="AL27" s="13"/>
-      <c r="AM27" s="14"/>
-      <c r="AN27" s="12"/>
-      <c r="AO27" s="9"/>
-      <c r="AP27" s="10"/>
-      <c r="AQ27" s="11"/>
-      <c r="AR27" s="12"/>
-      <c r="AS27" s="9"/>
-      <c r="AT27" s="10"/>
-      <c r="AU27" s="11"/>
-      <c r="AV27" s="12"/>
-      <c r="AW27" s="9"/>
-      <c r="AX27" s="10"/>
-      <c r="AY27" s="11"/>
-      <c r="AZ27" s="13"/>
-      <c r="BA27" s="14"/>
-      <c r="BB27" s="12"/>
-      <c r="BC27" s="9"/>
-      <c r="BD27" s="10"/>
-      <c r="BE27" s="11"/>
-      <c r="BF27" s="13"/>
-      <c r="BG27" s="14"/>
-      <c r="BH27" s="13"/>
-      <c r="BI27" s="14"/>
-      <c r="BJ27" s="13"/>
-      <c r="BK27" s="15"/>
-      <c r="BL27" s="9"/>
-      <c r="BM27" s="10"/>
-      <c r="BN27" s="11"/>
-      <c r="BO27" s="12"/>
-      <c r="BP27" s="9"/>
-      <c r="BQ27" s="10"/>
-      <c r="BR27" s="11"/>
-      <c r="BS27" s="13"/>
-      <c r="BT27" s="14"/>
-      <c r="BU27" s="13"/>
-      <c r="BV27" s="14"/>
-      <c r="BW27" s="12"/>
-      <c r="BX27" s="9"/>
-      <c r="BY27" s="10"/>
-      <c r="BZ27" s="11"/>
-      <c r="CA27" s="12"/>
-      <c r="CB27" s="9"/>
-      <c r="CC27" s="10"/>
-      <c r="CD27" s="11"/>
-      <c r="CE27" s="13"/>
-      <c r="CF27" s="14"/>
-      <c r="CG27" s="13"/>
-      <c r="CH27" s="14"/>
-      <c r="CI27" s="13"/>
-      <c r="CJ27" s="15"/>
+      <c r="AJ27" s="12"/>
+      <c r="AK27" s="9"/>
+      <c r="AL27" s="10"/>
+      <c r="AM27" s="11"/>
+      <c r="AN27" s="13"/>
+      <c r="AO27" s="14"/>
+      <c r="AP27" s="13"/>
+      <c r="AQ27" s="14"/>
+      <c r="AR27" s="13"/>
+      <c r="AS27" s="15"/>
+      <c r="AT27" s="9"/>
+      <c r="AU27" s="10"/>
+      <c r="AV27" s="11"/>
+      <c r="AW27" s="12"/>
+      <c r="AX27" s="9"/>
+      <c r="AY27" s="10"/>
+      <c r="AZ27" s="11"/>
+      <c r="BA27" s="13"/>
+      <c r="BB27" s="14"/>
+      <c r="BC27" s="13"/>
+      <c r="BD27" s="14"/>
+      <c r="BE27" s="12"/>
+      <c r="BF27" s="9"/>
+      <c r="BG27" s="10"/>
+      <c r="BH27" s="11"/>
+      <c r="BI27" s="12"/>
+      <c r="BJ27" s="9"/>
+      <c r="BK27" s="10"/>
+      <c r="BL27" s="11"/>
+      <c r="BM27" s="13"/>
+      <c r="BN27" s="14"/>
+      <c r="BO27" s="13"/>
+      <c r="BP27" s="14"/>
+      <c r="BQ27" s="13"/>
+      <c r="BR27" s="15"/>
     </row>
-    <row r="28" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="8" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="10"/>
@@ -4067,67 +3488,49 @@
       <c r="AG28" s="11"/>
       <c r="AH28" s="13"/>
       <c r="AI28" s="14"/>
-      <c r="AJ28" s="13"/>
-      <c r="AK28" s="14"/>
-      <c r="AL28" s="13"/>
-      <c r="AM28" s="14"/>
-      <c r="AN28" s="12"/>
-      <c r="AO28" s="9"/>
-      <c r="AP28" s="10"/>
-      <c r="AQ28" s="11"/>
-      <c r="AR28" s="12"/>
-      <c r="AS28" s="9"/>
-      <c r="AT28" s="10"/>
-      <c r="AU28" s="11"/>
-      <c r="AV28" s="12"/>
-      <c r="AW28" s="9"/>
-      <c r="AX28" s="10"/>
-      <c r="AY28" s="11"/>
-      <c r="AZ28" s="13"/>
-      <c r="BA28" s="14"/>
-      <c r="BB28" s="12"/>
-      <c r="BC28" s="9"/>
-      <c r="BD28" s="10"/>
-      <c r="BE28" s="11"/>
-      <c r="BF28" s="13"/>
-      <c r="BG28" s="14"/>
-      <c r="BH28" s="13"/>
-      <c r="BI28" s="14"/>
-      <c r="BJ28" s="13"/>
-      <c r="BK28" s="15"/>
-      <c r="BL28" s="9"/>
-      <c r="BM28" s="10"/>
-      <c r="BN28" s="11"/>
-      <c r="BO28" s="12"/>
-      <c r="BP28" s="9"/>
-      <c r="BQ28" s="10"/>
-      <c r="BR28" s="11"/>
-      <c r="BS28" s="13"/>
-      <c r="BT28" s="14"/>
-      <c r="BU28" s="13"/>
-      <c r="BV28" s="14"/>
-      <c r="BW28" s="12"/>
-      <c r="BX28" s="9"/>
-      <c r="BY28" s="10"/>
-      <c r="BZ28" s="11"/>
-      <c r="CA28" s="12"/>
-      <c r="CB28" s="9"/>
-      <c r="CC28" s="10"/>
-      <c r="CD28" s="11"/>
-      <c r="CE28" s="13"/>
-      <c r="CF28" s="14"/>
-      <c r="CG28" s="13"/>
-      <c r="CH28" s="14"/>
-      <c r="CI28" s="13"/>
-      <c r="CJ28" s="15"/>
+      <c r="AJ28" s="12"/>
+      <c r="AK28" s="9"/>
+      <c r="AL28" s="10"/>
+      <c r="AM28" s="11"/>
+      <c r="AN28" s="13"/>
+      <c r="AO28" s="14"/>
+      <c r="AP28" s="13"/>
+      <c r="AQ28" s="14"/>
+      <c r="AR28" s="13"/>
+      <c r="AS28" s="15"/>
+      <c r="AT28" s="9"/>
+      <c r="AU28" s="10"/>
+      <c r="AV28" s="11"/>
+      <c r="AW28" s="12"/>
+      <c r="AX28" s="9"/>
+      <c r="AY28" s="10"/>
+      <c r="AZ28" s="11"/>
+      <c r="BA28" s="13"/>
+      <c r="BB28" s="14"/>
+      <c r="BC28" s="13"/>
+      <c r="BD28" s="14"/>
+      <c r="BE28" s="12"/>
+      <c r="BF28" s="9"/>
+      <c r="BG28" s="10"/>
+      <c r="BH28" s="11"/>
+      <c r="BI28" s="12"/>
+      <c r="BJ28" s="9"/>
+      <c r="BK28" s="10"/>
+      <c r="BL28" s="11"/>
+      <c r="BM28" s="13"/>
+      <c r="BN28" s="14"/>
+      <c r="BO28" s="13"/>
+      <c r="BP28" s="14"/>
+      <c r="BQ28" s="13"/>
+      <c r="BR28" s="15"/>
     </row>
-    <row r="29" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="8" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="10"/>
@@ -4161,67 +3564,49 @@
       <c r="AG29" s="11"/>
       <c r="AH29" s="13"/>
       <c r="AI29" s="14"/>
-      <c r="AJ29" s="13"/>
-      <c r="AK29" s="14"/>
-      <c r="AL29" s="13"/>
-      <c r="AM29" s="14"/>
-      <c r="AN29" s="12"/>
-      <c r="AO29" s="9"/>
-      <c r="AP29" s="10"/>
-      <c r="AQ29" s="11"/>
-      <c r="AR29" s="12"/>
-      <c r="AS29" s="9"/>
-      <c r="AT29" s="10"/>
-      <c r="AU29" s="11"/>
-      <c r="AV29" s="12"/>
-      <c r="AW29" s="9"/>
-      <c r="AX29" s="10"/>
-      <c r="AY29" s="11"/>
-      <c r="AZ29" s="13"/>
-      <c r="BA29" s="14"/>
-      <c r="BB29" s="12"/>
-      <c r="BC29" s="9"/>
-      <c r="BD29" s="10"/>
-      <c r="BE29" s="11"/>
-      <c r="BF29" s="13"/>
-      <c r="BG29" s="14"/>
-      <c r="BH29" s="13"/>
-      <c r="BI29" s="14"/>
-      <c r="BJ29" s="13"/>
-      <c r="BK29" s="15"/>
-      <c r="BL29" s="9"/>
-      <c r="BM29" s="10"/>
-      <c r="BN29" s="11"/>
-      <c r="BO29" s="12"/>
-      <c r="BP29" s="9"/>
-      <c r="BQ29" s="10"/>
-      <c r="BR29" s="11"/>
-      <c r="BS29" s="13"/>
-      <c r="BT29" s="14"/>
-      <c r="BU29" s="13"/>
-      <c r="BV29" s="14"/>
-      <c r="BW29" s="12"/>
-      <c r="BX29" s="9"/>
-      <c r="BY29" s="10"/>
-      <c r="BZ29" s="11"/>
-      <c r="CA29" s="12"/>
-      <c r="CB29" s="9"/>
-      <c r="CC29" s="10"/>
-      <c r="CD29" s="11"/>
-      <c r="CE29" s="13"/>
-      <c r="CF29" s="14"/>
-      <c r="CG29" s="13"/>
-      <c r="CH29" s="14"/>
-      <c r="CI29" s="13"/>
-      <c r="CJ29" s="15"/>
+      <c r="AJ29" s="12"/>
+      <c r="AK29" s="9"/>
+      <c r="AL29" s="10"/>
+      <c r="AM29" s="11"/>
+      <c r="AN29" s="13"/>
+      <c r="AO29" s="14"/>
+      <c r="AP29" s="13"/>
+      <c r="AQ29" s="14"/>
+      <c r="AR29" s="13"/>
+      <c r="AS29" s="15"/>
+      <c r="AT29" s="9"/>
+      <c r="AU29" s="10"/>
+      <c r="AV29" s="11"/>
+      <c r="AW29" s="12"/>
+      <c r="AX29" s="9"/>
+      <c r="AY29" s="10"/>
+      <c r="AZ29" s="11"/>
+      <c r="BA29" s="13"/>
+      <c r="BB29" s="14"/>
+      <c r="BC29" s="13"/>
+      <c r="BD29" s="14"/>
+      <c r="BE29" s="12"/>
+      <c r="BF29" s="9"/>
+      <c r="BG29" s="10"/>
+      <c r="BH29" s="11"/>
+      <c r="BI29" s="12"/>
+      <c r="BJ29" s="9"/>
+      <c r="BK29" s="10"/>
+      <c r="BL29" s="11"/>
+      <c r="BM29" s="13"/>
+      <c r="BN29" s="14"/>
+      <c r="BO29" s="13"/>
+      <c r="BP29" s="14"/>
+      <c r="BQ29" s="13"/>
+      <c r="BR29" s="15"/>
     </row>
-    <row r="30" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="8" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="10"/>
@@ -4255,67 +3640,49 @@
       <c r="AG30" s="11"/>
       <c r="AH30" s="13"/>
       <c r="AI30" s="14"/>
-      <c r="AJ30" s="13"/>
-      <c r="AK30" s="14"/>
-      <c r="AL30" s="13"/>
-      <c r="AM30" s="14"/>
-      <c r="AN30" s="12"/>
-      <c r="AO30" s="9"/>
-      <c r="AP30" s="10"/>
-      <c r="AQ30" s="11"/>
-      <c r="AR30" s="12"/>
-      <c r="AS30" s="9"/>
-      <c r="AT30" s="10"/>
-      <c r="AU30" s="11"/>
-      <c r="AV30" s="12"/>
-      <c r="AW30" s="9"/>
-      <c r="AX30" s="10"/>
-      <c r="AY30" s="11"/>
-      <c r="AZ30" s="13"/>
-      <c r="BA30" s="14"/>
-      <c r="BB30" s="12"/>
-      <c r="BC30" s="9"/>
-      <c r="BD30" s="10"/>
-      <c r="BE30" s="11"/>
-      <c r="BF30" s="13"/>
-      <c r="BG30" s="14"/>
-      <c r="BH30" s="13"/>
-      <c r="BI30" s="14"/>
-      <c r="BJ30" s="13"/>
-      <c r="BK30" s="15"/>
-      <c r="BL30" s="9"/>
-      <c r="BM30" s="10"/>
-      <c r="BN30" s="11"/>
-      <c r="BO30" s="12"/>
-      <c r="BP30" s="9"/>
-      <c r="BQ30" s="10"/>
-      <c r="BR30" s="11"/>
-      <c r="BS30" s="13"/>
-      <c r="BT30" s="14"/>
-      <c r="BU30" s="13"/>
-      <c r="BV30" s="14"/>
-      <c r="BW30" s="12"/>
-      <c r="BX30" s="9"/>
-      <c r="BY30" s="10"/>
-      <c r="BZ30" s="11"/>
-      <c r="CA30" s="12"/>
-      <c r="CB30" s="9"/>
-      <c r="CC30" s="10"/>
-      <c r="CD30" s="11"/>
-      <c r="CE30" s="13"/>
-      <c r="CF30" s="14"/>
-      <c r="CG30" s="13"/>
-      <c r="CH30" s="14"/>
-      <c r="CI30" s="13"/>
-      <c r="CJ30" s="15"/>
+      <c r="AJ30" s="12"/>
+      <c r="AK30" s="9"/>
+      <c r="AL30" s="10"/>
+      <c r="AM30" s="11"/>
+      <c r="AN30" s="13"/>
+      <c r="AO30" s="14"/>
+      <c r="AP30" s="13"/>
+      <c r="AQ30" s="14"/>
+      <c r="AR30" s="13"/>
+      <c r="AS30" s="15"/>
+      <c r="AT30" s="9"/>
+      <c r="AU30" s="10"/>
+      <c r="AV30" s="11"/>
+      <c r="AW30" s="12"/>
+      <c r="AX30" s="9"/>
+      <c r="AY30" s="10"/>
+      <c r="AZ30" s="11"/>
+      <c r="BA30" s="13"/>
+      <c r="BB30" s="14"/>
+      <c r="BC30" s="13"/>
+      <c r="BD30" s="14"/>
+      <c r="BE30" s="12"/>
+      <c r="BF30" s="9"/>
+      <c r="BG30" s="10"/>
+      <c r="BH30" s="11"/>
+      <c r="BI30" s="12"/>
+      <c r="BJ30" s="9"/>
+      <c r="BK30" s="10"/>
+      <c r="BL30" s="11"/>
+      <c r="BM30" s="13"/>
+      <c r="BN30" s="14"/>
+      <c r="BO30" s="13"/>
+      <c r="BP30" s="14"/>
+      <c r="BQ30" s="13"/>
+      <c r="BR30" s="15"/>
     </row>
-    <row r="31" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="8" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="10"/>
@@ -4349,67 +3716,49 @@
       <c r="AG31" s="11"/>
       <c r="AH31" s="13"/>
       <c r="AI31" s="14"/>
-      <c r="AJ31" s="13"/>
-      <c r="AK31" s="14"/>
-      <c r="AL31" s="13"/>
-      <c r="AM31" s="14"/>
-      <c r="AN31" s="12"/>
-      <c r="AO31" s="9"/>
-      <c r="AP31" s="10"/>
-      <c r="AQ31" s="11"/>
-      <c r="AR31" s="12"/>
-      <c r="AS31" s="9"/>
-      <c r="AT31" s="10"/>
-      <c r="AU31" s="11"/>
-      <c r="AV31" s="12"/>
-      <c r="AW31" s="9"/>
-      <c r="AX31" s="10"/>
-      <c r="AY31" s="11"/>
-      <c r="AZ31" s="13"/>
-      <c r="BA31" s="14"/>
-      <c r="BB31" s="12"/>
-      <c r="BC31" s="9"/>
-      <c r="BD31" s="10"/>
-      <c r="BE31" s="11"/>
-      <c r="BF31" s="13"/>
-      <c r="BG31" s="14"/>
-      <c r="BH31" s="13"/>
-      <c r="BI31" s="14"/>
-      <c r="BJ31" s="13"/>
-      <c r="BK31" s="15"/>
-      <c r="BL31" s="9"/>
-      <c r="BM31" s="10"/>
-      <c r="BN31" s="11"/>
-      <c r="BO31" s="12"/>
-      <c r="BP31" s="9"/>
-      <c r="BQ31" s="10"/>
-      <c r="BR31" s="11"/>
-      <c r="BS31" s="13"/>
-      <c r="BT31" s="14"/>
-      <c r="BU31" s="13"/>
-      <c r="BV31" s="14"/>
-      <c r="BW31" s="12"/>
-      <c r="BX31" s="9"/>
-      <c r="BY31" s="10"/>
-      <c r="BZ31" s="11"/>
-      <c r="CA31" s="12"/>
-      <c r="CB31" s="9"/>
-      <c r="CC31" s="10"/>
-      <c r="CD31" s="11"/>
-      <c r="CE31" s="13"/>
-      <c r="CF31" s="14"/>
-      <c r="CG31" s="13"/>
-      <c r="CH31" s="14"/>
-      <c r="CI31" s="13"/>
-      <c r="CJ31" s="15"/>
+      <c r="AJ31" s="12"/>
+      <c r="AK31" s="9"/>
+      <c r="AL31" s="10"/>
+      <c r="AM31" s="11"/>
+      <c r="AN31" s="13"/>
+      <c r="AO31" s="14"/>
+      <c r="AP31" s="13"/>
+      <c r="AQ31" s="14"/>
+      <c r="AR31" s="13"/>
+      <c r="AS31" s="15"/>
+      <c r="AT31" s="9"/>
+      <c r="AU31" s="10"/>
+      <c r="AV31" s="11"/>
+      <c r="AW31" s="12"/>
+      <c r="AX31" s="9"/>
+      <c r="AY31" s="10"/>
+      <c r="AZ31" s="11"/>
+      <c r="BA31" s="13"/>
+      <c r="BB31" s="14"/>
+      <c r="BC31" s="13"/>
+      <c r="BD31" s="14"/>
+      <c r="BE31" s="12"/>
+      <c r="BF31" s="9"/>
+      <c r="BG31" s="10"/>
+      <c r="BH31" s="11"/>
+      <c r="BI31" s="12"/>
+      <c r="BJ31" s="9"/>
+      <c r="BK31" s="10"/>
+      <c r="BL31" s="11"/>
+      <c r="BM31" s="13"/>
+      <c r="BN31" s="14"/>
+      <c r="BO31" s="13"/>
+      <c r="BP31" s="14"/>
+      <c r="BQ31" s="13"/>
+      <c r="BR31" s="15"/>
     </row>
-    <row r="32" spans="1:88" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:70" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="8" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D32" s="9"/>
       <c r="E32" s="10"/>
@@ -4443,123 +3792,91 @@
       <c r="AG32" s="11"/>
       <c r="AH32" s="13"/>
       <c r="AI32" s="14"/>
-      <c r="AJ32" s="13"/>
-      <c r="AK32" s="14"/>
-      <c r="AL32" s="13"/>
-      <c r="AM32" s="14"/>
-      <c r="AN32" s="12"/>
-      <c r="AO32" s="9"/>
-      <c r="AP32" s="10"/>
-      <c r="AQ32" s="11"/>
-      <c r="AR32" s="12"/>
-      <c r="AS32" s="9"/>
-      <c r="AT32" s="10"/>
-      <c r="AU32" s="11"/>
-      <c r="AV32" s="12"/>
-      <c r="AW32" s="9"/>
-      <c r="AX32" s="10"/>
-      <c r="AY32" s="11"/>
-      <c r="AZ32" s="13"/>
-      <c r="BA32" s="14"/>
-      <c r="BB32" s="12"/>
-      <c r="BC32" s="9"/>
-      <c r="BD32" s="10"/>
-      <c r="BE32" s="11"/>
-      <c r="BF32" s="13"/>
-      <c r="BG32" s="14"/>
-      <c r="BH32" s="13"/>
-      <c r="BI32" s="14"/>
-      <c r="BJ32" s="13"/>
-      <c r="BK32" s="15"/>
-      <c r="BL32" s="9"/>
-      <c r="BM32" s="10"/>
-      <c r="BN32" s="11"/>
-      <c r="BO32" s="12"/>
-      <c r="BP32" s="9"/>
-      <c r="BQ32" s="10"/>
-      <c r="BR32" s="11"/>
-      <c r="BS32" s="13"/>
-      <c r="BT32" s="14"/>
-      <c r="BU32" s="13"/>
-      <c r="BV32" s="14"/>
-      <c r="BW32" s="12"/>
-      <c r="BX32" s="9"/>
-      <c r="BY32" s="10"/>
-      <c r="BZ32" s="11"/>
-      <c r="CA32" s="12"/>
-      <c r="CB32" s="9"/>
-      <c r="CC32" s="10"/>
-      <c r="CD32" s="11"/>
-      <c r="CE32" s="13"/>
-      <c r="CF32" s="14"/>
-      <c r="CG32" s="13"/>
-      <c r="CH32" s="14"/>
-      <c r="CI32" s="13"/>
-      <c r="CJ32" s="15"/>
+      <c r="AJ32" s="12"/>
+      <c r="AK32" s="9"/>
+      <c r="AL32" s="10"/>
+      <c r="AM32" s="11"/>
+      <c r="AN32" s="13"/>
+      <c r="AO32" s="14"/>
+      <c r="AP32" s="13"/>
+      <c r="AQ32" s="14"/>
+      <c r="AR32" s="13"/>
+      <c r="AS32" s="15"/>
+      <c r="AT32" s="9"/>
+      <c r="AU32" s="10"/>
+      <c r="AV32" s="11"/>
+      <c r="AW32" s="12"/>
+      <c r="AX32" s="9"/>
+      <c r="AY32" s="10"/>
+      <c r="AZ32" s="11"/>
+      <c r="BA32" s="13"/>
+      <c r="BB32" s="14"/>
+      <c r="BC32" s="13"/>
+      <c r="BD32" s="14"/>
+      <c r="BE32" s="12"/>
+      <c r="BF32" s="9"/>
+      <c r="BG32" s="10"/>
+      <c r="BH32" s="11"/>
+      <c r="BI32" s="12"/>
+      <c r="BJ32" s="9"/>
+      <c r="BK32" s="10"/>
+      <c r="BL32" s="11"/>
+      <c r="BM32" s="13"/>
+      <c r="BN32" s="14"/>
+      <c r="BO32" s="13"/>
+      <c r="BP32" s="14"/>
+      <c r="BQ32" s="13"/>
+      <c r="BR32" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="61">
+  <mergeCells count="47">
     <mergeCell ref="A1:A3"/>
-    <mergeCell ref="BZ2:BZ3"/>
+    <mergeCell ref="BH2:BH3"/>
     <mergeCell ref="U1:AD1"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="W2:W3"/>
     <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="BQ2:BQ3"/>
-    <mergeCell ref="BP1:BW1"/>
-    <mergeCell ref="AQ2:AQ3"/>
+    <mergeCell ref="AY2:AY3"/>
+    <mergeCell ref="AX1:BE1"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="C1:C3"/>
     <mergeCell ref="H1:P1"/>
-    <mergeCell ref="AS2:AS3"/>
-    <mergeCell ref="AU2:AU3"/>
-    <mergeCell ref="AO1:AR1"/>
-    <mergeCell ref="AS1:AV1"/>
     <mergeCell ref="R2:R3"/>
     <mergeCell ref="T2:T3"/>
     <mergeCell ref="V2:V3"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AR2:AR3"/>
-    <mergeCell ref="AT2:AT3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="I2:I3"/>
-    <mergeCell ref="BR2:BR3"/>
-    <mergeCell ref="AO2:AO3"/>
-    <mergeCell ref="BO2:BO3"/>
-    <mergeCell ref="BE2:BE3"/>
+    <mergeCell ref="AZ2:AZ3"/>
     <mergeCell ref="AW2:AW3"/>
-    <mergeCell ref="AY2:AY3"/>
-    <mergeCell ref="AW1:BB1"/>
-    <mergeCell ref="AX2:AX3"/>
+    <mergeCell ref="AM2:AM3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="AE1:AJ1"/>
+    <mergeCell ref="AF2:AF3"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B1:B3"/>
-    <mergeCell ref="CA2:CA3"/>
-    <mergeCell ref="AE1:AN1"/>
-    <mergeCell ref="BM2:BM3"/>
-    <mergeCell ref="BL2:BL3"/>
-    <mergeCell ref="AV2:AV3"/>
+    <mergeCell ref="BI2:BI3"/>
+    <mergeCell ref="AU2:AU3"/>
+    <mergeCell ref="AT2:AT3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="H2:H3"/>
-    <mergeCell ref="AP2:AP3"/>
-    <mergeCell ref="BL1:BO1"/>
-    <mergeCell ref="BX1:CA1"/>
-    <mergeCell ref="BN2:BN3"/>
-    <mergeCell ref="CD2:CD3"/>
+    <mergeCell ref="AT1:AW1"/>
+    <mergeCell ref="BF1:BI1"/>
+    <mergeCell ref="AV2:AV3"/>
+    <mergeCell ref="BL2:BL3"/>
     <mergeCell ref="Q1:T1"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="CB1:CJ1"/>
-    <mergeCell ref="CC2:CC3"/>
-    <mergeCell ref="BY2:BY3"/>
-    <mergeCell ref="BC2:BC3"/>
+    <mergeCell ref="BJ1:BR1"/>
+    <mergeCell ref="BK2:BK3"/>
+    <mergeCell ref="BG2:BG3"/>
+    <mergeCell ref="AK2:AK3"/>
     <mergeCell ref="S2:S3"/>
     <mergeCell ref="U2:U3"/>
-    <mergeCell ref="BX2:BX3"/>
-    <mergeCell ref="BP2:BP3"/>
-    <mergeCell ref="BC1:BK1"/>
-    <mergeCell ref="CB2:CB3"/>
-    <mergeCell ref="BD2:BD3"/>
+    <mergeCell ref="BF2:BF3"/>
+    <mergeCell ref="AX2:AX3"/>
+    <mergeCell ref="AK1:AS1"/>
+    <mergeCell ref="BJ2:BJ3"/>
+    <mergeCell ref="AL2:AL3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
